--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="X8Y4JVdIXEKLpDJP7hVAAYSTI5kjQzRrtR54ob+x3R4qc+Zd0ku8M7FvnP1nK+iil4XV3y1eJvAgcZCw8QOSGg==" workbookSaltValue="ZEZzRiQi1vWfMy4mrA+tRA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="845"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="845" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Jan" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="176">
   <si>
     <t>JAN</t>
   </si>
@@ -583,6 +583,39 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>betel</t>
+  </si>
+  <si>
+    <t>mensal</t>
+  </si>
+  <si>
+    <t>cannon</t>
+  </si>
+  <si>
+    <t>sitio</t>
+  </si>
+  <si>
+    <t>tenis</t>
+  </si>
+  <si>
+    <t>spotify</t>
+  </si>
+  <si>
+    <t>claro</t>
+  </si>
+  <si>
+    <t>ipva</t>
+  </si>
+  <si>
+    <t>gasolina pra manu</t>
+  </si>
+  <si>
+    <t>brasil</t>
+  </si>
+  <si>
+    <t>churrasco</t>
   </si>
 </sst>
 </file>
@@ -2320,7 +2353,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90</c:v>
+                  <c:v>142</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2329,16 +2362,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>86.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>217</c:v>
+                  <c:v>430.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2582,37 +2615,37 @@
                   <c:v>1546.57</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>1381.5499999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2725,7 +2758,7 @@
                   <c:v>905.0200000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>923.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2845,37 +2878,37 @@
                   <c:v>641.54999999999984</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999975</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>641.54999999999984</c:v>
+                  <c:v>457.76999999999981</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2891,11 +2924,11 @@
         </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="-24"/>
-        <c:axId val="1317015104"/>
-        <c:axId val="1317010208"/>
+        <c:axId val="185348784"/>
+        <c:axId val="185358032"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1317015104"/>
+        <c:axId val="185348784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2937,7 +2970,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1317010208"/>
+        <c:crossAx val="185358032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2945,7 +2978,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1317010208"/>
+        <c:axId val="185358032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2995,7 +3028,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1317015104"/>
+        <c:crossAx val="185348784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4608,7 +4641,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5762,7 +5795,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -5783,7 +5816,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5821,11 +5854,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Set!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -6796,7 +6829,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -6817,7 +6850,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6855,11 +6888,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Out!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7828,7 +7861,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -7850,7 +7883,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
       <c r="N4"/>
     </row>
@@ -7891,11 +7924,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Nov!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="N7"/>
     </row>
@@ -8971,51 +9004,51 @@
       </c>
       <c r="D3" s="41">
         <f>Fev!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>1381.5499999999997</v>
       </c>
       <c r="E3" s="41">
         <f>Mar!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F3" s="41">
         <f>Abr!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="G3" s="41">
         <f>Mai!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="H3" s="41">
         <f>Jun!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="41">
         <f>Jul!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="J3" s="41">
         <f>Ago!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="K3" s="41">
         <f>Set!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="L3" s="41">
         <f>Out!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="M3" s="41">
         <f>Nov!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="N3" s="103">
         <f>Dez!$F$3</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="O3" s="103">
         <f>SUM(C3:N3)</f>
-        <v>8603.6200000000008</v>
+        <v>7505.8199999999961</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
@@ -9028,7 +9061,7 @@
       </c>
       <c r="D4" s="43">
         <f>Fev!$F$4</f>
-        <v>0</v>
+        <v>561.57999999999993</v>
       </c>
       <c r="E4" s="43">
         <f>Mar!$F$4</f>
@@ -9072,7 +9105,7 @@
       </c>
       <c r="O4" s="104">
         <f t="shared" ref="O4:O8" si="0">SUM(C4:N4)</f>
-        <v>568.0200000000001</v>
+        <v>1129.5999999999999</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
@@ -9085,7 +9118,7 @@
       </c>
       <c r="D5" s="44">
         <f>Fev!$F$6</f>
-        <v>0</v>
+        <v>362.2</v>
       </c>
       <c r="E5" s="44">
         <f>Mar!$F$6</f>
@@ -9129,7 +9162,7 @@
       </c>
       <c r="O5" s="105">
         <f t="shared" si="0"/>
-        <v>337</v>
+        <v>699.2</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
@@ -9142,7 +9175,7 @@
       </c>
       <c r="D6" s="45">
         <f t="shared" ref="D6:N6" si="1">D4+D5</f>
-        <v>0</v>
+        <v>923.78</v>
       </c>
       <c r="E6" s="45">
         <f t="shared" si="1"/>
@@ -9186,7 +9219,7 @@
       </c>
       <c r="O6" s="106">
         <f t="shared" si="0"/>
-        <v>905.0200000000001</v>
+        <v>1828.8000000000002</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
@@ -9199,51 +9232,51 @@
       </c>
       <c r="D7" s="102">
         <f t="shared" ref="D7:N7" si="2">D3-D6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999975</v>
       </c>
       <c r="E7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="G7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="H7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="J7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="K7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="L7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="M7" s="102">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="N7" s="107">
         <f t="shared" si="2"/>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="O7" s="107">
         <f t="shared" si="0"/>
-        <v>7698.5999999999995</v>
+        <v>5677.0199999999977</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9417,7 +9450,7 @@
       </c>
       <c r="D15" s="115">
         <f>Fev!$B$42</f>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E15" s="114">
         <f>Mar!$B$42</f>
@@ -9461,7 +9494,7 @@
       </c>
       <c r="O15" s="122">
         <f t="shared" ref="O15:O20" si="3">SUM(C15:N15)</f>
-        <v>23.69</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
@@ -9474,7 +9507,7 @@
       </c>
       <c r="D16" s="115">
         <f>Fev!B51</f>
-        <v>0</v>
+        <v>226.24</v>
       </c>
       <c r="E16" s="114">
         <f>Mar!$B$51</f>
@@ -9518,7 +9551,7 @@
       </c>
       <c r="O16" s="122">
         <f t="shared" si="3"/>
-        <v>93.95</v>
+        <v>320.19</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
@@ -9531,7 +9564,7 @@
       </c>
       <c r="D17" s="115">
         <f>Fev!$B$59</f>
-        <v>0</v>
+        <v>296.33999999999997</v>
       </c>
       <c r="E17" s="114">
         <f>Mar!$B$59</f>
@@ -9575,7 +9608,7 @@
       </c>
       <c r="O17" s="122">
         <f t="shared" si="3"/>
-        <v>72</v>
+        <v>368.34</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
@@ -9798,7 +9831,7 @@
       </c>
       <c r="G26" s="69">
         <f>SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
-        <v>90</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
@@ -9842,7 +9875,7 @@
       </c>
       <c r="G29" s="69">
         <f>SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
-        <v>30</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
@@ -9867,7 +9900,7 @@
     <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="73">
         <f>SUM(D30:D37)</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>22</v>
@@ -9881,7 +9914,7 @@
       </c>
       <c r="G31" s="69">
         <f>SUBTOTAL(9,Jan!I41,Fev!I41,Mar!I41,Abr!I41,Mai!I41,Jun!I41,Jul!I41,Ago!I41,Set!I41,Out!I41,Nov!I41,Dez!I41)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
@@ -9898,7 +9931,7 @@
       </c>
       <c r="G32" s="69">
         <f>SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
-        <v>217</v>
+        <v>430.5</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
@@ -9942,7 +9975,7 @@
       </c>
       <c r="D35" s="69">
         <f>SUBTOTAL(9,Fev!D46,Fev!D46,Mar!D46,Abr!D46,Mai!D46,Jun!D46,Jul!D46,Ago!D46,Set!D46,Out!D46,Nov!D46,Dez!D46)</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F35" s="80"/>
       <c r="G35" s="71">
@@ -9986,7 +10019,7 @@
     <row r="40" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="73">
         <f>SUM(D39:D45)</f>
-        <v>0</v>
+        <v>452.48</v>
       </c>
       <c r="C40" s="68" t="s">
         <v>83</v>
@@ -10033,7 +10066,7 @@
       </c>
       <c r="D44" s="69">
         <f>SUBTOTAL(9,Fev!D55,Fev!D55,Mar!D55,Abr!D55,Mai!D55,Jun!D55,Jul!D55,Ago!D55,Set!D55,Out!D55,Nov!D55,Dez!D55)</f>
-        <v>0</v>
+        <v>452.48</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10064,7 +10097,7 @@
     <row r="48" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="73">
         <f>SUM(D47:D53)</f>
-        <v>0</v>
+        <v>592.67999999999995</v>
       </c>
       <c r="C48" s="68" t="s">
         <v>32</v>
@@ -10101,7 +10134,7 @@
       </c>
       <c r="D51" s="69">
         <f>SUBTOTAL(9,Fev!D62,Fev!D62,Mar!D62,Abr!D62,Mai!D62,Jun!D62,Jul!D62,Ago!D62,Set!D62,Out!D62,Nov!D62,Dez!D62)</f>
-        <v>0</v>
+        <v>115.84</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -10111,7 +10144,7 @@
       </c>
       <c r="D52" s="69">
         <f>SUBTOTAL(9,Fev!D63,Fev!D63,Mar!D63,Abr!D63,Mai!D63,Jun!D63,Jul!D63,Ago!D63,Set!D63,Out!D63,Nov!D63,Dez!D63)</f>
-        <v>0</v>
+        <v>476.84</v>
       </c>
     </row>
     <row r="53" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11532,10 +11565,12 @@
         <v>4</v>
       </c>
       <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
+      <c r="D3" s="30">
+        <v>740</v>
+      </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>1381.5499999999997</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -11552,11 +11587,11 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>0</v>
+        <v>561.57999999999993</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11581,7 +11616,7 @@
       <c r="D6" s="27"/>
       <c r="F6" s="36">
         <f>SUM(K11:K22)</f>
-        <v>0</v>
+        <v>362.2</v>
       </c>
       <c r="I6" s="14">
         <v>45847</v>
@@ -11598,7 +11633,7 @@
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -11663,75 +11698,168 @@
       <c r="P10" s="60"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="33"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="60"/>
+      <c r="B11" s="21">
+        <v>46064</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="33">
+        <f>39+135</f>
+        <v>174</v>
+      </c>
+      <c r="H11" s="18">
+        <v>46054</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="K11" s="60">
+        <v>40</v>
+      </c>
       <c r="M11" s="77"/>
       <c r="N11" s="96"/>
       <c r="O11" s="87"/>
       <c r="P11" s="61"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="22"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="34"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="61"/>
+      <c r="B12" s="22">
+        <v>46066</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" s="34">
+        <v>238.42</v>
+      </c>
+      <c r="H12" s="19">
+        <v>46055</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="61">
+        <f>25.1+31.6</f>
+        <v>56.7</v>
+      </c>
       <c r="M12" s="77"/>
       <c r="N12" s="96"/>
       <c r="O12" s="87"/>
       <c r="P12" s="61"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="22"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="34"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="61"/>
+      <c r="B13" s="22">
+        <v>46066</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="34">
+        <v>57.92</v>
+      </c>
+      <c r="H13" s="19">
+        <v>46062</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K13" s="61">
+        <v>143.5</v>
+      </c>
       <c r="M13" s="77"/>
       <c r="N13" s="96"/>
       <c r="O13" s="87"/>
       <c r="P13" s="61"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="22"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="34"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="61"/>
+      <c r="B14" s="22">
+        <v>46068</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="34">
+        <f>37.14+15.1</f>
+        <v>52.24</v>
+      </c>
+      <c r="H14" s="19">
+        <v>46062</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="61">
+        <v>70</v>
+      </c>
       <c r="M14" s="77"/>
       <c r="N14" s="96"/>
       <c r="O14" s="87"/>
       <c r="P14" s="61"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="34"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="61"/>
+      <c r="B15" s="22">
+        <v>46081</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="34">
+        <v>39</v>
+      </c>
+      <c r="H15" s="19">
+        <v>46063</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K15" s="61">
+        <v>7</v>
+      </c>
       <c r="M15" s="77"/>
       <c r="N15" s="96"/>
       <c r="O15" s="87"/>
@@ -11743,10 +11871,18 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="34"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="61"/>
+      <c r="H16" s="19">
+        <v>46064</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="61">
+        <v>30</v>
+      </c>
       <c r="M16" s="77"/>
       <c r="N16" s="96"/>
       <c r="O16" s="87"/>
@@ -11758,10 +11894,18 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="34"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="61"/>
+      <c r="H17" s="19">
+        <v>46065</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K17" s="61">
+        <v>15</v>
+      </c>
       <c r="M17" s="77"/>
       <c r="N17" s="96"/>
       <c r="O17" s="87"/>
@@ -11961,7 +12105,7 @@
       </c>
       <c r="I36" s="69">
         <f t="shared" ref="I36:I45" si="1">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
@@ -12007,7 +12151,7 @@
       </c>
       <c r="I39" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12037,13 +12181,13 @@
       </c>
       <c r="I41" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="73">
         <f>SUBTOTAL(9,D41:D48)</f>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C42" s="68" t="s">
         <v>22</v>
@@ -12057,7 +12201,7 @@
       </c>
       <c r="I42" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
@@ -12112,7 +12256,7 @@
       </c>
       <c r="D46" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
@@ -12147,7 +12291,7 @@
     <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="108">
         <f>SUM(D50:D56)</f>
-        <v>0</v>
+        <v>226.24</v>
       </c>
       <c r="C51" s="68" t="s">
         <v>83</v>
@@ -12190,7 +12334,7 @@
       </c>
       <c r="D55" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>226.24</v>
       </c>
     </row>
     <row r="56" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12218,7 +12362,7 @@
     <row r="59" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="73">
         <f>SUM(D58:D64)</f>
-        <v>0</v>
+        <v>296.33999999999997</v>
       </c>
       <c r="C59" s="68" t="s">
         <v>32</v>
@@ -12252,7 +12396,7 @@
       </c>
       <c r="D62" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>57.92</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -12261,7 +12405,7 @@
       </c>
       <c r="D63" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>238.42</v>
       </c>
     </row>
     <row r="64" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12486,7 +12630,7 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="H9:K9"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D32">
       <formula1>INDIRECT(C11)</formula1>
     </dataValidation>
@@ -12494,7 +12638,7 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Modelo!$P$3:$P$10</xm:f>
@@ -12524,7 +12668,7 @@
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
@@ -12561,7 +12705,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -12582,7 +12726,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12620,11 +12764,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Fev!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -13587,7 +13731,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -13608,7 +13752,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13646,11 +13790,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mar!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -14613,7 +14757,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -14634,7 +14778,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14672,11 +14816,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Abr!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -15639,7 +15783,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -15660,7 +15804,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15698,11 +15842,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mai!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -16665,7 +16809,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -16686,7 +16830,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16724,11 +16868,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jun!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -17716,7 +17860,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -17739,7 +17883,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17777,11 +17921,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jul!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -18840,7 +18984,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -18861,7 +19005,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18899,11 +19043,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Ago!F7</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>641.54999999999984</v>
+        <v>457.76999999999981</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="182">
   <si>
     <t>JAN</t>
   </si>
@@ -616,6 +616,24 @@
   </si>
   <si>
     <t>churrasco</t>
+  </si>
+  <si>
+    <t>Bernardo</t>
+  </si>
+  <si>
+    <t>aiversario do Be</t>
+  </si>
+  <si>
+    <t>pasta, calculadora</t>
+  </si>
+  <si>
+    <t>relação</t>
+  </si>
+  <si>
+    <t>monster</t>
+  </si>
+  <si>
+    <t>balaclava</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2320,9 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -2350,10 +2370,10 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>142</c:v>
+                  <c:v>256.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2362,16 +2382,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>86.7</c:v>
+                  <c:v>142.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>430.5</c:v>
+                  <c:v>580</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2615,37 +2635,37 @@
                   <c:v>1546.57</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1381.5499999999997</c:v>
+                  <c:v>1581.5499999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>1157.7699999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2761,7 +2781,7 @@
                   <c:v>923.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>746.23</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2878,37 +2898,37 @@
                   <c:v>641.54999999999984</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>457.76999999999975</c:v>
+                  <c:v>657.76999999999975</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>457.76999999999981</c:v>
+                  <c:v>411.53999999999974</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2924,11 +2944,11 @@
         </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="-24"/>
-        <c:axId val="185348784"/>
-        <c:axId val="185358032"/>
+        <c:axId val="1857149744"/>
+        <c:axId val="1857151920"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="185348784"/>
+        <c:axId val="1857149744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2970,7 +2990,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="185358032"/>
+        <c:crossAx val="1857151920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2978,7 +2998,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="185358032"/>
+        <c:axId val="1857151920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3028,7 +3048,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="185348784"/>
+        <c:crossAx val="1857149744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3079,6 +3099,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4641,7 +4662,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5795,7 +5816,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -5816,7 +5837,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5854,11 +5875,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Set!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -6829,7 +6850,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -6850,7 +6871,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6888,11 +6909,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Out!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7861,7 +7882,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -7883,7 +7904,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="N4"/>
     </row>
@@ -7924,11 +7945,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Nov!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="N7"/>
     </row>
@@ -8938,7 +8959,7 @@
     <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="48" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="48" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.7109375" style="48" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" style="48" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.7109375" style="48" customWidth="1"/>
@@ -9004,51 +9025,51 @@
       </c>
       <c r="D3" s="41">
         <f>Fev!$F$3</f>
-        <v>1381.5499999999997</v>
+        <v>1581.5499999999997</v>
       </c>
       <c r="E3" s="41">
         <f>Mar!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>1157.7699999999998</v>
       </c>
       <c r="F3" s="41">
         <f>Abr!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="G3" s="41">
         <f>Mai!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="H3" s="41">
         <f>Jun!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="41">
         <f>Jul!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="J3" s="41">
         <f>Ago!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="K3" s="41">
         <f>Set!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="L3" s="41">
         <f>Out!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="M3" s="41">
         <f>Nov!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="N3" s="103">
         <f>Dez!$F$3</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="O3" s="103">
         <f>SUM(C3:N3)</f>
-        <v>7505.8199999999961</v>
+        <v>7989.7499999999991</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
@@ -9065,7 +9086,7 @@
       </c>
       <c r="E4" s="43">
         <f>Mar!$F$4</f>
-        <v>0</v>
+        <v>311.63</v>
       </c>
       <c r="F4" s="43">
         <f>Abr!$F$4</f>
@@ -9105,7 +9126,7 @@
       </c>
       <c r="O4" s="104">
         <f t="shared" ref="O4:O8" si="0">SUM(C4:N4)</f>
-        <v>1129.5999999999999</v>
+        <v>1441.23</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
@@ -9122,7 +9143,7 @@
       </c>
       <c r="E5" s="44">
         <f>Mar!$F$6</f>
-        <v>0</v>
+        <v>434.6</v>
       </c>
       <c r="F5" s="44">
         <f>Abr!$F$6</f>
@@ -9162,7 +9183,7 @@
       </c>
       <c r="O5" s="105">
         <f t="shared" si="0"/>
-        <v>699.2</v>
+        <v>1133.8000000000002</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
@@ -9179,7 +9200,7 @@
       </c>
       <c r="E6" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>746.23</v>
       </c>
       <c r="F6" s="45">
         <f t="shared" si="1"/>
@@ -9219,7 +9240,7 @@
       </c>
       <c r="O6" s="106">
         <f t="shared" si="0"/>
-        <v>1828.8000000000002</v>
+        <v>2575.0300000000002</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
@@ -9232,51 +9253,51 @@
       </c>
       <c r="D7" s="102">
         <f t="shared" ref="D7:N7" si="2">D3-D6</f>
-        <v>457.76999999999975</v>
+        <v>657.76999999999975</v>
       </c>
       <c r="E7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="G7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="H7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="J7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="K7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="L7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="M7" s="102">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="N7" s="107">
         <f t="shared" si="2"/>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="O7" s="107">
         <f t="shared" si="0"/>
-        <v>5677.0199999999977</v>
+        <v>5414.7199999999984</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9289,7 +9310,7 @@
       </c>
       <c r="D8" s="100">
         <f>Fev!D4</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E8" s="100">
         <f>Mar!D4</f>
@@ -9333,7 +9354,7 @@
       </c>
       <c r="O8" s="101">
         <f t="shared" si="0"/>
-        <v>103.33</v>
+        <v>303.33</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9454,7 +9475,7 @@
       </c>
       <c r="E15" s="114">
         <f>Mar!$B$42</f>
-        <v>0</v>
+        <v>47.879999999999995</v>
       </c>
       <c r="F15" s="115">
         <f>Abr!$B$42</f>
@@ -9494,7 +9515,7 @@
       </c>
       <c r="O15" s="122">
         <f t="shared" ref="O15:O20" si="3">SUM(C15:N15)</f>
-        <v>62.69</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
@@ -9511,7 +9532,7 @@
       </c>
       <c r="E16" s="114">
         <f>Mar!$B$51</f>
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="F16" s="115">
         <f>Abr!$B$51</f>
@@ -9551,7 +9572,7 @@
       </c>
       <c r="O16" s="122">
         <f t="shared" si="3"/>
-        <v>320.19</v>
+        <v>339.49</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
@@ -9568,7 +9589,7 @@
       </c>
       <c r="E17" s="114">
         <f>Mar!$B$59</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="F17" s="115">
         <f>Abr!$B$59</f>
@@ -9608,7 +9629,7 @@
       </c>
       <c r="O17" s="122">
         <f t="shared" si="3"/>
-        <v>368.34</v>
+        <v>578.33999999999992</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
@@ -9625,7 +9646,7 @@
       </c>
       <c r="E18" s="114">
         <f>Mar!$B$67</f>
-        <v>0</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="F18" s="115">
         <f>Abr!$B$67</f>
@@ -9665,7 +9686,7 @@
       </c>
       <c r="O18" s="122">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>34.450000000000003</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
@@ -9814,7 +9835,7 @@
       </c>
       <c r="G25" s="67">
         <f>SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
@@ -9831,7 +9852,7 @@
       </c>
       <c r="G26" s="69">
         <f>SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
-        <v>142</v>
+        <v>256.3</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
@@ -9875,7 +9896,7 @@
       </c>
       <c r="G29" s="69">
         <f>SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
-        <v>86.7</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
@@ -9887,20 +9908,20 @@
       </c>
       <c r="D30" s="67">
         <f>SUBTOTAL(9,Fev!D41,Fev!D41,Mar!D41,Abr!D41,Mai!D41,Jun!D41,Jul!D41,Ago!D41,Set!D41,Out!D41,Nov!D41,Dez!D41)</f>
-        <v>0</v>
+        <v>47.879999999999995</v>
       </c>
       <c r="F30" s="79" t="s">
         <v>111</v>
       </c>
       <c r="G30" s="69">
         <f>SUBTOTAL(9,Jan!I40,Fev!I40,Mar!I40,Abr!I40,Mai!I40,Jun!I40,Jul!I40,Ago!I40,Set!I40,Out!I40,Nov!I40,Dez!I40)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="73">
         <f>SUM(D30:D37)</f>
-        <v>78</v>
+        <v>125.88</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>22</v>
@@ -9931,7 +9952,7 @@
       </c>
       <c r="G32" s="69">
         <f>SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
-        <v>430.5</v>
+        <v>580</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
@@ -10019,7 +10040,7 @@
     <row r="40" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="73">
         <f>SUM(D39:D45)</f>
-        <v>452.48</v>
+        <v>471.78000000000003</v>
       </c>
       <c r="C40" s="68" t="s">
         <v>83</v>
@@ -10046,7 +10067,7 @@
       </c>
       <c r="D42" s="69">
         <f>SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
@@ -10097,7 +10118,7 @@
     <row r="48" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="73">
         <f>SUM(D47:D53)</f>
-        <v>592.67999999999995</v>
+        <v>802.68000000000006</v>
       </c>
       <c r="C48" s="68" t="s">
         <v>32</v>
@@ -10134,7 +10155,7 @@
       </c>
       <c r="D51" s="69">
         <f>SUBTOTAL(9,Fev!D62,Fev!D62,Mar!D62,Abr!D62,Mai!D62,Jun!D62,Jul!D62,Ago!D62,Set!D62,Out!D62,Nov!D62,Dez!D62)</f>
-        <v>115.84</v>
+        <v>325.84000000000003</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -10175,7 +10196,7 @@
     <row r="56" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="73">
         <f>SUM(D55:D61)</f>
-        <v>0</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="C56" s="68" t="s">
         <v>90</v>
@@ -10192,7 +10213,7 @@
       </c>
       <c r="D57" s="69">
         <f>SUBTOTAL(9,Fev!D68,Fev!D68,Mar!D68,Abr!D68,Mai!D68,Jun!D68,Jul!D68,Ago!D68,Set!D68,Out!D68,Nov!D68,Dez!D68)</f>
-        <v>0</v>
+        <v>34.450000000000003</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
@@ -11531,14 +11552,17 @@
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11.85546875" customWidth="1"/>
-    <col min="13" max="16" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -11570,7 +11594,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1381.5499999999997</v>
+        <v>1581.5499999999997</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -11583,7 +11607,7 @@
       <c r="C4" s="7"/>
       <c r="D4" s="26">
         <f>SUM(P10:P25)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
@@ -11591,7 +11615,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11602,7 +11626,7 @@
       <c r="D5" s="27"/>
       <c r="F5" s="98">
         <f>D4</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>7</v>
@@ -11633,7 +11657,7 @@
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>657.76999999999975</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -11692,10 +11716,18 @@
       <c r="K10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M10" s="89"/>
-      <c r="N10" s="95"/>
-      <c r="O10" s="90"/>
-      <c r="P10" s="60"/>
+      <c r="M10" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="N10" s="95">
+        <v>46081</v>
+      </c>
+      <c r="O10" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="P10" s="60">
+        <v>200</v>
+      </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
@@ -12669,8 +12701,8 @@
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -12702,10 +12734,12 @@
         <v>4</v>
       </c>
       <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
+      <c r="D3" s="30">
+        <v>500</v>
+      </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>1157.7699999999998</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -12722,11 +12756,11 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>0</v>
+        <v>311.63</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12742,6 +12776,10 @@
       <c r="I5" s="17" t="s">
         <v>7</v>
       </c>
+      <c r="K5">
+        <f>405/6</f>
+        <v>67.5</v>
+      </c>
     </row>
     <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="24" t="s">
@@ -12751,7 +12789,7 @@
       <c r="D6" s="27"/>
       <c r="F6" s="36">
         <f>SUM(K11:K22)</f>
-        <v>0</v>
+        <v>434.6</v>
       </c>
       <c r="I6" s="14">
         <v>45847</v>
@@ -12764,11 +12802,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Fev!F7</f>
-        <v>457.76999999999981</v>
+        <v>657.76999999999975</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -12833,75 +12871,160 @@
       <c r="P10" s="60"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="33"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="13"/>
+      <c r="B11" s="21">
+        <v>46083</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="33">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="H11" s="18">
+        <v>46084</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="J11" s="13"/>
-      <c r="K11" s="60"/>
+      <c r="K11" s="60">
+        <v>55.8</v>
+      </c>
       <c r="M11" s="77"/>
       <c r="N11" s="96"/>
       <c r="O11" s="87"/>
       <c r="P11" s="61"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="22"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="34"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="61"/>
+      <c r="B12" s="22">
+        <v>46087</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="34">
+        <v>210</v>
+      </c>
+      <c r="H12" s="19">
+        <v>46088</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K12" s="61">
+        <v>6.8</v>
+      </c>
       <c r="M12" s="77"/>
       <c r="N12" s="96"/>
       <c r="O12" s="87"/>
       <c r="P12" s="61"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="22"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="34"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="13"/>
+      <c r="B13" s="22">
+        <v>46088</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="34">
+        <f>8.44*2</f>
+        <v>16.88</v>
+      </c>
+      <c r="H13" s="19">
+        <v>46088</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="61"/>
+      <c r="K13" s="61">
+        <v>30</v>
+      </c>
       <c r="M13" s="77"/>
       <c r="N13" s="96"/>
       <c r="O13" s="87"/>
       <c r="P13" s="61"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="22"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="34"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="13"/>
+      <c r="B14" s="22">
+        <v>46088</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" s="34">
+        <v>31</v>
+      </c>
+      <c r="H14" s="19">
+        <v>46089</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="61"/>
+      <c r="K14" s="61">
+        <v>50</v>
+      </c>
       <c r="M14" s="77"/>
       <c r="N14" s="96"/>
       <c r="O14" s="87"/>
       <c r="P14" s="61"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="34"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="61"/>
+      <c r="B15" s="22">
+        <v>46092</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F15" s="34">
+        <v>19.3</v>
+      </c>
+      <c r="H15" s="19">
+        <v>46099</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K15" s="61">
+        <v>40</v>
+      </c>
       <c r="M15" s="77"/>
       <c r="N15" s="96"/>
       <c r="O15" s="87"/>
@@ -12913,10 +13036,18 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="34"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="61"/>
+      <c r="H16" s="19">
+        <v>46091</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K16" s="61">
+        <v>149.5</v>
+      </c>
       <c r="M16" s="77"/>
       <c r="N16" s="96"/>
       <c r="O16" s="87"/>
@@ -12928,10 +13059,16 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="34"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="13"/>
+      <c r="H17" s="19">
+        <v>46103</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>107</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="61"/>
+      <c r="K17" s="61">
+        <v>67.5</v>
+      </c>
       <c r="M17" s="77"/>
       <c r="N17" s="96"/>
       <c r="O17" s="87"/>
@@ -12943,10 +13080,16 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="34"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="13"/>
+      <c r="H18" s="19">
+        <v>46101</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>140</v>
+      </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="61"/>
+      <c r="K18" s="61">
+        <v>35</v>
+      </c>
       <c r="M18" s="77"/>
       <c r="N18" s="96"/>
       <c r="O18" s="87"/>
@@ -13111,7 +13254,7 @@
       </c>
       <c r="I35" s="67">
         <f>SUMIF($I$11:$I$22,H35,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13131,7 +13274,7 @@
       </c>
       <c r="I36" s="69">
         <f t="shared" ref="I36:I45" si="1">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>0</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
@@ -13177,7 +13320,7 @@
       </c>
       <c r="I39" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13188,7 +13331,7 @@
       </c>
       <c r="I40" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
@@ -13200,7 +13343,7 @@
       </c>
       <c r="D41" s="67">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47.879999999999995</v>
       </c>
       <c r="H41" s="79" t="s">
         <v>112</v>
@@ -13213,7 +13356,7 @@
     <row r="42" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="73">
         <f>SUBTOTAL(9,D41:D48)</f>
-        <v>0</v>
+        <v>47.879999999999995</v>
       </c>
       <c r="C42" s="68" t="s">
         <v>22</v>
@@ -13227,7 +13370,7 @@
       </c>
       <c r="I42" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
@@ -13317,7 +13460,7 @@
     <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="73">
         <f>SUM(D50:D56)</f>
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="C51" s="68" t="s">
         <v>83</v>
@@ -13342,7 +13485,7 @@
       </c>
       <c r="D53" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -13388,7 +13531,7 @@
     <row r="59" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="73">
         <f>SUM(D58:D64)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C59" s="68" t="s">
         <v>32</v>
@@ -13422,7 +13565,7 @@
       </c>
       <c r="D62" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -13459,7 +13602,7 @@
     <row r="67" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="73">
         <f>SUM(D66:D72)</f>
-        <v>0</v>
+        <v>34.450000000000003</v>
       </c>
       <c r="C67" s="68" t="s">
         <v>90</v>
@@ -13475,7 +13618,7 @@
       </c>
       <c r="D68" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34.450000000000003</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
@@ -13731,7 +13874,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -13752,7 +13895,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13790,11 +13933,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mar!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -14757,7 +14900,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -14778,7 +14921,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14816,11 +14959,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Abr!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -15783,7 +15926,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -15804,7 +15947,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15842,11 +15985,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mai!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -16809,7 +16952,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -16830,7 +16973,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16868,11 +17011,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jun!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -17860,7 +18003,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -17883,7 +18026,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17921,11 +18064,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jul!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -18984,7 +19127,7 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -19005,7 +19148,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19043,11 +19186,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Ago!F7</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>457.76999999999981</v>
+        <v>411.53999999999974</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="839" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="839" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Jan" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="198">
   <si>
     <t>JAN</t>
   </si>
@@ -671,16 +671,16 @@
     <t>para passar o mês, tenho =&gt;</t>
   </si>
   <si>
-    <t>11 notas de cem para depositar</t>
+    <t>jo e livro</t>
   </si>
   <si>
-    <t>5 notas de 100 para depositar</t>
+    <t>acai</t>
   </si>
   <si>
-    <t>268 em dinheiro</t>
+    <t>camisa campeonato</t>
   </si>
   <si>
-    <t>6,72 no banco</t>
+    <t>gasolina pra são joao</t>
   </si>
 </sst>
 </file>
@@ -1749,21 +1749,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1829,6 +1814,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1993,28 +1993,28 @@
                   <c:v>2542.5399999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2133,7 +2133,7 @@
                   <c:v>1638.23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>677.5</c:v>
+                  <c:v>900.06</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2253,31 +2253,31 @@
                   <c:v>442.53999999999951</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1865.0399999999995</c:v>
+                  <c:v>1642.4799999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2293,11 +2293,11 @@
         </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="-24"/>
-        <c:axId val="1066573344"/>
-        <c:axId val="1066571168"/>
+        <c:axId val="-2067426848"/>
+        <c:axId val="-2067414336"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1066573344"/>
+        <c:axId val="-2067426848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2339,7 +2339,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1066571168"/>
+        <c:crossAx val="-2067414336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2347,7 +2347,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1066571168"/>
+        <c:axId val="-2067414336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2397,7 +2397,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1066573344"/>
+        <c:crossAx val="-2067426848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2448,7 +2448,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3103,9 +3102,7 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -4736,10 +4733,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -4759,10 +4756,10 @@
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -4782,12 +4779,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -4818,10 +4815,10 @@
       <c r="I6" s="14">
         <v>46026</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
@@ -4834,19 +4831,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>157</v>
       </c>
@@ -5938,10 +5935,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -5951,15 +5948,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -5976,12 +5973,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -6010,10 +6007,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -6022,28 +6019,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Set!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -6989,10 +6986,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -7002,15 +6999,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -7027,12 +7024,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -7061,10 +7058,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -7073,28 +7070,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Out!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -8037,10 +8034,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
       <c r="N2"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8051,15 +8048,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
       <c r="N3"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8077,12 +8074,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
       <c r="N4"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8113,10 +8110,10 @@
       <c r="I6" s="14">
         <v>46002</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
       <c r="N6"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8126,11 +8123,11 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Nov!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="N7"/>
     </row>
@@ -8138,19 +8135,19 @@
       <c r="N8"/>
     </row>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -9201,451 +9198,454 @@
       <c r="B3" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="128">
+      <c r="C3" s="123">
         <f>Jan!$F$3</f>
         <v>2246.5699999999997</v>
       </c>
-      <c r="D3" s="129">
+      <c r="D3" s="124">
         <f>Fev!$F$3</f>
         <v>2281.5499999999997</v>
       </c>
-      <c r="E3" s="129">
+      <c r="E3" s="124">
         <f>Mar!$F$3</f>
         <v>2080.7699999999995</v>
       </c>
-      <c r="F3" s="129">
+      <c r="F3" s="124">
         <f>Abr!$F$3</f>
         <v>2542.5399999999995</v>
       </c>
-      <c r="G3" s="129">
+      <c r="G3" s="124">
         <f>Mai!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="H3" s="129">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="H3" s="124">
         <f>Jun!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="I3" s="129">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="I3" s="124">
         <f>Jul!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="J3" s="129">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="J3" s="124">
         <f>Ago!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="K3" s="129">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="K3" s="124">
         <f>Set!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="L3" s="129">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="L3" s="124">
         <f>Out!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="M3" s="129">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="M3" s="124">
         <f>Nov!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="N3" s="130">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="N3" s="125">
         <f>Dez!$F$3</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="O3" s="130">
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="O3" s="125">
         <f>SUM(C3:N3)</f>
-        <v>24071.75</v>
+        <v>22291.269999999993</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="131">
+      <c r="C4" s="126">
         <f>Jan!$F$4</f>
         <v>568.0200000000001</v>
       </c>
-      <c r="D4" s="131">
+      <c r="D4" s="126">
         <f>Fev!$F$4</f>
         <v>561.57999999999993</v>
       </c>
-      <c r="E4" s="131">
+      <c r="E4" s="126">
         <f>Mar!$F$4</f>
         <v>1203.6300000000001</v>
       </c>
-      <c r="F4" s="131">
+      <c r="F4" s="126">
         <f>Abr!$F$4</f>
-        <v>202.5</v>
-      </c>
-      <c r="G4" s="131">
+        <v>390.06</v>
+      </c>
+      <c r="G4" s="126">
         <f>Mai!$F$4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="131">
+      <c r="H4" s="126">
         <f>Jun!$F$4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="131">
+      <c r="I4" s="126">
         <f>Jul!$F$4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="131">
+      <c r="J4" s="126">
         <f>Ago!$F$4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="131">
+      <c r="K4" s="126">
         <f>Set!$F$4</f>
         <v>0</v>
       </c>
-      <c r="L4" s="131">
+      <c r="L4" s="126">
         <f>Out!$F$4</f>
         <v>0</v>
       </c>
-      <c r="M4" s="131">
+      <c r="M4" s="126">
         <f>Nov!$F$4</f>
         <v>0</v>
       </c>
-      <c r="N4" s="132">
+      <c r="N4" s="127">
         <f>Dez!$F$4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="132">
+      <c r="O4" s="127">
         <f t="shared" ref="O4:O10" si="0">SUM(C4:N4)</f>
-        <v>2535.73</v>
+        <v>2723.29</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="133">
+      <c r="C5" s="128">
         <f>Jan!$F$6</f>
         <v>337</v>
       </c>
-      <c r="D5" s="133">
+      <c r="D5" s="128">
         <f>Fev!$F$6</f>
         <v>362.2</v>
       </c>
-      <c r="E5" s="133">
+      <c r="E5" s="128">
         <f>Mar!$F$6</f>
         <v>434.6</v>
       </c>
-      <c r="F5" s="133">
+      <c r="F5" s="128">
         <f>Abr!$F$6</f>
-        <v>475</v>
-      </c>
-      <c r="G5" s="133">
+        <v>510</v>
+      </c>
+      <c r="G5" s="128">
         <f>Mai!$F$6</f>
         <v>0</v>
       </c>
-      <c r="H5" s="133">
+      <c r="H5" s="128">
         <f>Jun!$F$6</f>
         <v>0</v>
       </c>
-      <c r="I5" s="133">
+      <c r="I5" s="128">
         <f>Jul!$F$6</f>
         <v>0</v>
       </c>
-      <c r="J5" s="133">
+      <c r="J5" s="128">
         <f>Ago!$F$6</f>
         <v>0</v>
       </c>
-      <c r="K5" s="133">
+      <c r="K5" s="128">
         <f>Set!$F$6</f>
         <v>0</v>
       </c>
-      <c r="L5" s="133">
+      <c r="L5" s="128">
         <f>Out!$F$6</f>
         <v>0</v>
       </c>
-      <c r="M5" s="133">
+      <c r="M5" s="128">
         <f>Nov!$F$6</f>
         <v>0</v>
       </c>
-      <c r="N5" s="134">
+      <c r="N5" s="129">
         <f>Dez!$F$6</f>
         <v>0</v>
       </c>
-      <c r="O5" s="134">
-        <f t="shared" si="0"/>
-        <v>1608.8000000000002</v>
+      <c r="O5" s="129">
+        <f t="shared" si="0"/>
+        <v>1643.8000000000002</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="124">
+      <c r="C6" s="119">
         <f>Jan!$L$3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="124">
+      <c r="D6" s="119">
         <f>Fev!$L$3</f>
         <v>0</v>
       </c>
-      <c r="E6" s="124">
+      <c r="E6" s="119">
         <f>Mar!$L$3</f>
         <v>0</v>
       </c>
-      <c r="F6" s="124">
+      <c r="F6" s="119">
         <f>Abr!$L$3</f>
         <v>1385.57</v>
       </c>
-      <c r="G6" s="124">
+      <c r="G6" s="119">
         <f>Mai!$L$3</f>
         <v>0</v>
       </c>
-      <c r="H6" s="124">
+      <c r="H6" s="119">
         <f>Jun!$L$3</f>
         <v>0</v>
       </c>
-      <c r="I6" s="124">
+      <c r="I6" s="119">
         <f>Jul!$L$3</f>
         <v>0</v>
       </c>
-      <c r="J6" s="124">
+      <c r="J6" s="119">
         <f>Ago!$L$3</f>
         <v>0</v>
       </c>
-      <c r="K6" s="124">
+      <c r="K6" s="119">
         <f>Set!$L$3</f>
         <v>0</v>
       </c>
-      <c r="L6" s="124">
+      <c r="L6" s="119">
         <f>Out!$L$3</f>
         <v>0</v>
       </c>
-      <c r="M6" s="124">
+      <c r="M6" s="119">
         <f>Nov!$L$3</f>
         <v>0</v>
       </c>
-      <c r="N6" s="125">
+      <c r="N6" s="120">
         <f>Dez!$L$3</f>
         <v>0</v>
       </c>
-      <c r="O6" s="135"/>
+      <c r="O6" s="130">
+        <f>SUM(C6:N6)</f>
+        <v>1385.57</v>
+      </c>
     </row>
     <row r="7" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="126">
+      <c r="C7" s="121">
         <f>Jan!$L$4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="126">
+      <c r="D7" s="121">
         <f>Fev!$L$4</f>
         <v>0</v>
       </c>
-      <c r="E7" s="126">
+      <c r="E7" s="121">
         <f>Mar!$L$4</f>
         <v>0</v>
       </c>
-      <c r="F7" s="126">
+      <c r="F7" s="121">
         <f>Abr!$L$4</f>
         <v>1185.57</v>
       </c>
-      <c r="G7" s="126">
+      <c r="G7" s="121">
         <f>Mai!$L$4</f>
         <v>0</v>
       </c>
-      <c r="H7" s="126">
+      <c r="H7" s="121">
         <f>Jun!$L$4</f>
         <v>0</v>
       </c>
-      <c r="I7" s="126">
+      <c r="I7" s="121">
         <f>Jul!$L$4</f>
         <v>0</v>
       </c>
-      <c r="J7" s="126">
+      <c r="J7" s="121">
         <f>Ago!$L$4</f>
         <v>0</v>
       </c>
-      <c r="K7" s="126">
+      <c r="K7" s="121">
         <f>Set!$L$4</f>
         <v>0</v>
       </c>
-      <c r="L7" s="126">
+      <c r="L7" s="121">
         <f>Out!$L$4</f>
         <v>0</v>
       </c>
-      <c r="M7" s="126">
+      <c r="M7" s="121">
         <f>Nov!$L$4</f>
         <v>0</v>
       </c>
-      <c r="N7" s="127">
+      <c r="N7" s="122">
         <f>Dez!$L$4</f>
         <v>0</v>
       </c>
-      <c r="O7" s="136">
-        <f>N7</f>
-        <v>0</v>
+      <c r="O7" s="131">
+        <f>SUM(C7:N7)</f>
+        <v>1185.57</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="137">
-        <f>C4+C5</f>
+      <c r="C8" s="132">
+        <f t="shared" ref="C8:N8" si="1">C4+C5</f>
         <v>905.0200000000001</v>
       </c>
-      <c r="D8" s="137">
-        <f>D4+D5</f>
+      <c r="D8" s="132">
+        <f t="shared" si="1"/>
         <v>923.78</v>
       </c>
-      <c r="E8" s="137">
-        <f>E4+E5</f>
+      <c r="E8" s="132">
+        <f t="shared" si="1"/>
         <v>1638.23</v>
       </c>
-      <c r="F8" s="137">
-        <f>F4+F5</f>
-        <v>677.5</v>
-      </c>
-      <c r="G8" s="137">
-        <f>G4+G5</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="137">
-        <f>H4+H5</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="137">
-        <f>I4+I5</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="137">
-        <f>J4+J5</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="137">
-        <f>K4+K5</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="137">
-        <f>L4+L5</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="137">
-        <f>M4+M5</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="138">
-        <f>N4+N5</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="138">
-        <f t="shared" si="0"/>
-        <v>4144.5300000000007</v>
+      <c r="F8" s="132">
+        <f t="shared" si="1"/>
+        <v>900.06</v>
+      </c>
+      <c r="G8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="133">
+        <f t="shared" si="0"/>
+        <v>4367.09</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="139">
-        <f>C3-C8</f>
+      <c r="C9" s="134">
+        <f t="shared" ref="C9:N9" si="2">C3-C8</f>
         <v>1341.5499999999997</v>
       </c>
-      <c r="D9" s="139">
-        <f>D3-D8</f>
+      <c r="D9" s="134">
+        <f t="shared" si="2"/>
         <v>1357.7699999999998</v>
       </c>
-      <c r="E9" s="139">
-        <f>E3-E8</f>
+      <c r="E9" s="134">
+        <f t="shared" si="2"/>
         <v>442.53999999999951</v>
       </c>
-      <c r="F9" s="139">
-        <f>F3-F8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="G9" s="139">
-        <f>G3-G8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="H9" s="139">
-        <f>H3-H8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="I9" s="139">
-        <f>I3-I8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="J9" s="139">
-        <f>J3-J8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="K9" s="139">
-        <f>K3-K8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="L9" s="139">
-        <f>L3-L8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="M9" s="139">
-        <f>M3-M8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="N9" s="140">
-        <f>N3-N8</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="O9" s="140">
-        <f t="shared" si="0"/>
-        <v>19927.219999999994</v>
+      <c r="F9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="G9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="H9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="I9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="J9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="K9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="L9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="M9" s="134">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="N9" s="135">
+        <f t="shared" si="2"/>
+        <v>1642.4799999999996</v>
+      </c>
+      <c r="O9" s="135">
+        <f>N9</f>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="94" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="141">
+      <c r="C10" s="136">
         <f>Jan!D4</f>
         <v>103.33</v>
       </c>
-      <c r="D10" s="141">
+      <c r="D10" s="136">
         <f>Fev!D4</f>
         <v>200</v>
       </c>
-      <c r="E10" s="141">
+      <c r="E10" s="136">
         <f>Mar!D4</f>
         <v>0</v>
       </c>
-      <c r="F10" s="141">
+      <c r="F10" s="136">
         <f>Abr!D4</f>
         <v>0</v>
       </c>
-      <c r="G10" s="141">
+      <c r="G10" s="136">
         <f>Mai!D4</f>
         <v>0</v>
       </c>
-      <c r="H10" s="141">
+      <c r="H10" s="136">
         <f>Jun!D4</f>
         <v>0</v>
       </c>
-      <c r="I10" s="141">
+      <c r="I10" s="136">
         <f>Jul!D4</f>
         <v>0</v>
       </c>
-      <c r="J10" s="141">
+      <c r="J10" s="136">
         <f>Ago!D4</f>
         <v>0</v>
       </c>
-      <c r="K10" s="141">
+      <c r="K10" s="136">
         <f>Set!D4</f>
         <v>0</v>
       </c>
-      <c r="L10" s="141">
+      <c r="L10" s="136">
         <f>Out!D4</f>
         <v>0</v>
       </c>
-      <c r="M10" s="141">
+      <c r="M10" s="136">
         <f>Nov!D4</f>
         <v>0</v>
       </c>
-      <c r="N10" s="142">
+      <c r="N10" s="137">
         <f>Dez!D4</f>
         <v>0</v>
       </c>
-      <c r="O10" s="142">
+      <c r="O10" s="137">
         <f t="shared" si="0"/>
         <v>303.33</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F16" s="98">
         <f>Abr!$B$36</f>
-        <v>47.5</v>
+        <v>70.86</v>
       </c>
       <c r="G16" s="97">
         <f>Mai!$B$36</f>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="O16" s="108">
         <f>SUM(C16:N16)</f>
-        <v>59.5</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="109">
-        <f t="shared" ref="O17:O22" si="1">SUM(C17:N17)</f>
+        <f t="shared" ref="O17:O22" si="3">SUM(C17:N17)</f>
         <v>265.57</v>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="F18" s="102">
         <f>Abr!$B$51</f>
-        <v>0</v>
+        <v>115.7</v>
       </c>
       <c r="G18" s="101">
         <f>Mai!$B$51</f>
@@ -9864,8 +9864,8 @@
         <v>0</v>
       </c>
       <c r="O18" s="109">
-        <f t="shared" si="1"/>
-        <v>339.49</v>
+        <f t="shared" si="3"/>
+        <v>455.19</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="F19" s="102">
         <f>Abr!$B$59</f>
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="G19" s="101">
         <f>Mai!$B$59</f>
@@ -9921,8 +9921,8 @@
         <v>0</v>
       </c>
       <c r="O19" s="109">
-        <f t="shared" si="1"/>
-        <v>578.33999999999992</v>
+        <f t="shared" si="3"/>
+        <v>626.83999999999992</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
@@ -9978,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>34.450000000000003</v>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>880</v>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D26" s="62">
         <f>SUBTOTAL(9,Fev!D35,Fev!D35,Mar!D35,Abr!D35,Mai!D35,Jun!D35,Jul!D35,Ago!D35,Set!D35,Out!D35,Nov!D35,Dez!D35)</f>
-        <v>0</v>
+        <v>23.36</v>
       </c>
       <c r="F26"/>
       <c r="G26"/>
@@ -10114,7 +10114,7 @@
     <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="68">
         <f>SUM(D26:D30)</f>
-        <v>59.5</v>
+        <v>82.86</v>
       </c>
       <c r="C27" s="63" t="s">
         <v>75</v>
@@ -10333,7 +10333,7 @@
     <row r="42" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="68">
         <f>SUM(D41:D47)</f>
-        <v>471.78000000000003</v>
+        <v>587.48</v>
       </c>
       <c r="C42" s="63" t="s">
         <v>83</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="D44" s="64">
         <f>SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
-        <v>19.3</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
@@ -10411,7 +10411,7 @@
     <row r="50" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="68">
         <f>SUM(D49:D55)</f>
-        <v>802.68000000000006</v>
+        <v>851.18000000000006</v>
       </c>
       <c r="C50" s="63" t="s">
         <v>32</v>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D53" s="64">
         <f>SUBTOTAL(9,Fev!D62,Fev!D62,Mar!D62,Abr!D62,Mai!D62,Jun!D62,Jul!D62,Ago!D62,Set!D62,Out!D62,Nov!D62,Dez!D62)</f>
-        <v>325.84000000000003</v>
+        <v>374.34000000000003</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -10868,19 +10868,19 @@
       </c>
     </row>
     <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="N9" s="49"/>
       <c r="P9" s="52" t="s">
         <v>79</v>
@@ -11874,10 +11874,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -11894,10 +11894,10 @@
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -11948,10 +11948,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -11969,19 +11969,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -13036,10 +13036,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -13056,10 +13056,10 @@
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -13116,10 +13116,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -13137,19 +13137,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -14214,10 +14214,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -14234,14 +14234,11 @@
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123">
+      <c r="L3" s="118">
         <v>1385.57</v>
-      </c>
-      <c r="M3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14255,20 +14252,17 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>202.5</v>
+        <v>390.06</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123">
+      <c r="L4" s="118">
         <v>1185.57</v>
-      </c>
-      <c r="M4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14296,19 +14290,17 @@
       <c r="D6" s="27"/>
       <c r="F6" s="36">
         <f>SUM(K11:K22)</f>
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="I6" s="14">
         <v>46123</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144">
-        <v>274.72000000000003</v>
-      </c>
-      <c r="M6" t="s">
-        <v>196</v>
+      <c r="L6" s="139">
+        <f>274.72-67.7-23.36-48-48.5</f>
+        <v>87.160000000000025</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14322,27 +14314,24 @@
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
-      </c>
-      <c r="M7" t="s">
-        <v>197</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -14487,11 +14476,22 @@
       <c r="P13" s="56"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="22"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="34"/>
+      <c r="B14" s="22">
+        <v>46124</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F14" s="34">
+        <f>3.78+1.78+62.14</f>
+        <v>67.7</v>
+      </c>
       <c r="H14" s="19">
         <v>46123</v>
       </c>
@@ -14510,11 +14510,21 @@
       <c r="P14" s="56"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="34"/>
+      <c r="B15" s="22">
+        <v>46124</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" s="34">
+        <v>23.36</v>
+      </c>
       <c r="H15" s="19">
         <v>46123</v>
       </c>
@@ -14533,26 +14543,52 @@
       <c r="P15" s="56"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="22"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="34"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="13"/>
+      <c r="B16" s="22">
+        <v>46132</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" s="34">
+        <v>48</v>
+      </c>
+      <c r="H16" s="19">
+        <v>46130</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>140</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="56"/>
+      <c r="K16" s="56">
+        <v>35</v>
+      </c>
       <c r="M16" s="72"/>
       <c r="N16" s="91"/>
       <c r="O16" s="82"/>
       <c r="P16" s="56"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="22"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="34"/>
+      <c r="B17" s="22">
+        <v>46133</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F17" s="34">
+        <v>48.5</v>
+      </c>
       <c r="H17" s="19"/>
       <c r="I17" s="13"/>
       <c r="J17" s="1"/>
@@ -14645,7 +14681,7 @@
       <c r="F23" s="34"/>
       <c r="K23" s="116">
         <f>SUM(K11:K22)</f>
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="M23" s="72"/>
       <c r="N23" s="91"/>
@@ -14733,7 +14769,7 @@
       </c>
       <c r="D35" s="62">
         <f>SUMIF($D$11:$D$32,C35,$F$11:$F$32)</f>
-        <v>0</v>
+        <v>23.36</v>
       </c>
       <c r="H35" s="73" t="s">
         <v>106</v>
@@ -14746,7 +14782,7 @@
     <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="68">
         <f>SUM(D35:D39)</f>
-        <v>47.5</v>
+        <v>70.86</v>
       </c>
       <c r="C36" s="63" t="s">
         <v>75</v>
@@ -14946,7 +14982,7 @@
     <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="68">
         <f>SUM(D50:D56)</f>
-        <v>0</v>
+        <v>115.7</v>
       </c>
       <c r="C51" s="63" t="s">
         <v>83</v>
@@ -14971,7 +15007,7 @@
       </c>
       <c r="D53" s="64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -15017,7 +15053,7 @@
     <row r="59" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="68">
         <f>SUM(D58:D64)</f>
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="C59" s="63" t="s">
         <v>32</v>
@@ -15051,7 +15087,7 @@
       </c>
       <c r="D62" s="64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -15323,9 +15359,9 @@
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -15348,10 +15384,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -15361,15 +15397,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -15386,12 +15422,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -15420,10 +15456,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -15432,28 +15468,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Abr!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -16391,10 +16427,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -16404,15 +16440,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -16429,12 +16465,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -16463,10 +16499,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -16475,28 +16511,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mai!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -17434,10 +17470,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -17447,15 +17483,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -17472,12 +17508,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -17506,10 +17542,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -17518,28 +17554,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jun!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -18501,10 +18537,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -18514,15 +18550,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -18541,12 +18577,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -18575,10 +18611,10 @@
       <c r="I6" s="14">
         <v>45879</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -18587,28 +18623,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jul!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>
@@ -19642,10 +19678,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -19655,15 +19691,15 @@
       <c r="D3" s="30"/>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="L3" s="123"/>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -19680,12 +19716,12 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
-      </c>
-      <c r="K4" s="122" t="s">
+        <v>46133</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -19714,10 +19750,10 @@
       <c r="I6" s="14">
         <v>45847</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="144"/>
+      <c r="L6" s="139"/>
     </row>
     <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -19726,28 +19762,28 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Ago!F7</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>1865.0399999999995</v>
+        <v>1642.4799999999996</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
       <c r="M9" s="86" t="s">
         <v>124</v>
       </c>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="227">
   <si>
     <t>JAN</t>
   </si>
@@ -713,6 +713,60 @@
   </si>
   <si>
     <t xml:space="preserve">tenho </t>
+  </si>
+  <si>
+    <t>dinheiro para investimento futuro</t>
+  </si>
+  <si>
+    <t>mae</t>
+  </si>
+  <si>
+    <t>pc - processador</t>
+  </si>
+  <si>
+    <t>MONITOR</t>
+  </si>
+  <si>
+    <t>MOUSE</t>
+  </si>
+  <si>
+    <t>FONTE</t>
+  </si>
+  <si>
+    <t>TECLADO</t>
+  </si>
+  <si>
+    <t>dinheiro para inVestimento futuro</t>
+  </si>
+  <si>
+    <t>pichau</t>
+  </si>
+  <si>
+    <t>aliepres</t>
+  </si>
+  <si>
+    <t>aliespres</t>
+  </si>
+  <si>
+    <t>mousepad</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>kabum</t>
+  </si>
+  <si>
+    <t>terabyte</t>
+  </si>
+  <si>
+    <t>COOLER</t>
+  </si>
+  <si>
+    <t>amazon OU shoope</t>
   </si>
 </sst>
 </file>
@@ -723,7 +777,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,8 +859,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -954,6 +1016,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1597,7 +1665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1960,16 +2028,7 @@
     <xf numFmtId="44" fontId="0" fillId="25" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="25" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1983,6 +2042,23 @@
     </xf>
     <xf numFmtId="44" fontId="9" fillId="24" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="25" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="25" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2007,6 +2083,18 @@
     </xf>
     <xf numFmtId="44" fontId="10" fillId="22" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="22" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="22" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="26" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="26" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2669,7 +2757,7 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>300.10000000000002</c:v>
+                  <c:v>330.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2681,13 +2769,13 @@
                   <c:v>302.22000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>260</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>730</c:v>
+                  <c:v>877</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3682,10 +3770,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -3734,7 +3822,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -3802,19 +3890,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>135</v>
       </c>
@@ -4921,10 +5009,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -4937,7 +5025,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -4965,7 +5053,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -5024,31 +5112,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Set!F7</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -5999,10 +6087,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -6015,7 +6103,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -6043,7 +6131,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -6102,31 +6190,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Out!F7</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -7082,10 +7170,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
       <c r="N2"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7099,7 +7187,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -7128,7 +7216,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -7190,14 +7278,14 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Nov!F7</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="N7"/>
     </row>
@@ -7205,19 +7293,19 @@
       <c r="N8"/>
     </row>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -8223,39 +8311,39 @@
       </c>
       <c r="G3" s="124">
         <f>Mai!$F$3</f>
-        <v>1459.2399999999993</v>
+        <v>3109.2399999999993</v>
       </c>
       <c r="H3" s="124">
         <f>Jun!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>769.81999999999925</v>
       </c>
       <c r="I3" s="124">
         <f>Jul!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="J3" s="124">
         <f>Ago!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="K3" s="124">
         <f>Set!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="L3" s="124">
         <f>Out!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="M3" s="124">
         <f>Nov!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="N3" s="125">
         <f>Dez!$F$3</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="O3" s="125">
         <f>SUM(C3:N3)</f>
-        <v>10444.209999999994</v>
+        <v>15685.909999999996</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8280,11 +8368,11 @@
       </c>
       <c r="G4" s="126">
         <f>Mai!$F$4</f>
-        <v>1420.69</v>
+        <v>1840.5900000000001</v>
       </c>
       <c r="H4" s="126">
         <f>Jun!$F$4</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I4" s="126">
         <f>Jul!$F$4</f>
@@ -8312,7 +8400,7 @@
       </c>
       <c r="O4" s="127">
         <f t="shared" ref="O4:O10" si="0">SUM(C4:N4)</f>
-        <v>4477.0300000000007</v>
+        <v>5246.93</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8337,7 +8425,7 @@
       </c>
       <c r="G5" s="128">
         <f>Mai!$F$6</f>
-        <v>81.83</v>
+        <v>498.83</v>
       </c>
       <c r="H5" s="128">
         <f>Jun!$F$6</f>
@@ -8369,7 +8457,7 @@
       </c>
       <c r="O5" s="129">
         <f t="shared" si="0"/>
-        <v>1732.3200000000002</v>
+        <v>2149.3200000000002</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8394,11 +8482,11 @@
       </c>
       <c r="G6" s="119">
         <f>Mai!$L$3</f>
-        <v>1563</v>
+        <v>2503</v>
       </c>
       <c r="H6" s="119">
         <f>Jun!$L$3</f>
-        <v>0</v>
+        <v>2503</v>
       </c>
       <c r="I6" s="119">
         <f>Jul!$L$3</f>
@@ -8426,7 +8514,7 @@
       </c>
       <c r="O6" s="130">
         <f>SUM(C6:N6)</f>
-        <v>2906</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8508,11 +8596,11 @@
       </c>
       <c r="G8" s="132">
         <f t="shared" si="1"/>
-        <v>1502.52</v>
+        <v>2339.42</v>
       </c>
       <c r="H8" s="132">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I8" s="132">
         <f t="shared" si="1"/>
@@ -8540,7 +8628,7 @@
       </c>
       <c r="O8" s="133">
         <f t="shared" si="0"/>
-        <v>6209.35</v>
+        <v>7396.25</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8565,39 +8653,39 @@
       </c>
       <c r="G9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000655</v>
+        <v>769.81999999999925</v>
       </c>
       <c r="H9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="J9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="K9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="L9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="M9" s="134">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="N9" s="135">
         <f t="shared" si="2"/>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="O9" s="135">
         <f>N9</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -8840,7 +8928,7 @@
       </c>
       <c r="G18" s="101">
         <f>Mai!$B$51</f>
-        <v>0</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="H18" s="102">
         <f>Jun!$B$51</f>
@@ -8872,7 +8960,7 @@
       </c>
       <c r="O18" s="109">
         <f t="shared" si="3"/>
-        <v>492.69</v>
+        <v>562.59</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
@@ -9155,15 +9243,15 @@
         <f>SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
         <v>30</v>
       </c>
-      <c r="I28" s="171" t="s">
+      <c r="I28" s="175" t="s">
         <v>194</v>
       </c>
-      <c r="J28" s="172"/>
-      <c r="K28" s="172"/>
-      <c r="L28" s="173"/>
+      <c r="J28" s="176"/>
+      <c r="K28" s="176"/>
+      <c r="L28" s="177"/>
       <c r="M28" s="155">
-        <f>SUM(M30:M39)</f>
-        <v>-389.93999999999988</v>
+        <f>SUM(L30:L39)-SUM(K30:K39)</f>
+        <v>610.05999999999995</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -9180,21 +9268,21 @@
       </c>
       <c r="G29" s="64">
         <f>SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
-        <v>300.10000000000002</v>
-      </c>
-      <c r="I29" s="163" t="s">
+        <v>330.1</v>
+      </c>
+      <c r="I29" s="160" t="s">
         <v>195</v>
       </c>
-      <c r="J29" s="164" t="s">
+      <c r="J29" s="161" t="s">
         <v>201</v>
       </c>
-      <c r="K29" s="164" t="s">
+      <c r="K29" s="161" t="s">
         <v>196</v>
       </c>
-      <c r="L29" s="164" t="s">
+      <c r="L29" s="161" t="s">
         <v>197</v>
       </c>
-      <c r="M29" s="165" t="s">
+      <c r="M29" s="162" t="s">
         <v>198</v>
       </c>
     </row>
@@ -9220,14 +9308,14 @@
       <c r="J30" s="101" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="160">
+      <c r="K30" s="158">
         <v>201.64</v>
       </c>
       <c r="L30" s="156">
         <f>200.05+10+10+64</f>
         <v>284.05</v>
       </c>
-      <c r="M30" s="162">
+      <c r="M30" s="159">
         <f>L30-K30</f>
         <v>82.410000000000025</v>
       </c>
@@ -9252,13 +9340,13 @@
       <c r="J31" s="101" t="s">
         <v>203</v>
       </c>
-      <c r="K31" s="160">
+      <c r="K31" s="158">
         <v>1289.99</v>
       </c>
       <c r="L31" s="156">
         <v>1517.64</v>
       </c>
-      <c r="M31" s="162">
+      <c r="M31" s="159">
         <f t="shared" ref="M31:M39" si="4">L31-K31</f>
         <v>227.65000000000009</v>
       </c>
@@ -9280,13 +9368,15 @@
       <c r="J32" s="101" t="s">
         <v>205</v>
       </c>
-      <c r="K32" s="160">
+      <c r="K32" s="158">
         <v>700</v>
       </c>
-      <c r="L32" s="156"/>
-      <c r="M32" s="162">
+      <c r="L32" s="156">
+        <v>1000</v>
+      </c>
+      <c r="M32" s="159">
         <f t="shared" si="4"/>
-        <v>-700</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
@@ -9305,13 +9395,13 @@
       </c>
       <c r="G33" s="64">
         <f>SUBTOTAL(9,Jan!I40,Fev!I40,Mar!I40,Abr!I40,Mai!I40,Jun!I40,Jul!I40,Ago!I40,Set!I40,Out!I40,Nov!I40,Dez!I40)</f>
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="I33" s="157"/>
       <c r="J33" s="101"/>
-      <c r="K33" s="160"/>
+      <c r="K33" s="158"/>
       <c r="L33" s="156"/>
-      <c r="M33" s="162">
+      <c r="M33" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9337,9 +9427,9 @@
       </c>
       <c r="I34" s="157"/>
       <c r="J34" s="101"/>
-      <c r="K34" s="160"/>
+      <c r="K34" s="158"/>
       <c r="L34" s="156"/>
-      <c r="M34" s="162">
+      <c r="M34" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9358,13 +9448,13 @@
       </c>
       <c r="G35" s="64">
         <f>SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
-        <v>730</v>
+        <v>877</v>
       </c>
       <c r="I35" s="157"/>
       <c r="J35" s="101"/>
-      <c r="K35" s="160"/>
+      <c r="K35" s="158"/>
       <c r="L35" s="156"/>
-      <c r="M35" s="162">
+      <c r="M35" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9387,9 +9477,9 @@
       </c>
       <c r="I36" s="157"/>
       <c r="J36" s="101"/>
-      <c r="K36" s="160"/>
+      <c r="K36" s="158"/>
       <c r="L36" s="156"/>
-      <c r="M36" s="162">
+      <c r="M36" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9412,9 +9502,9 @@
       </c>
       <c r="I37" s="157"/>
       <c r="J37" s="101"/>
-      <c r="K37" s="160"/>
+      <c r="K37" s="158"/>
       <c r="L37" s="156"/>
-      <c r="M37" s="162">
+      <c r="M37" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9435,9 +9525,9 @@
       </c>
       <c r="I38" s="157"/>
       <c r="J38" s="101"/>
-      <c r="K38" s="160"/>
+      <c r="K38" s="158"/>
       <c r="L38" s="156"/>
-      <c r="M38" s="162">
+      <c r="M38" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9449,22 +9539,32 @@
         <f>SUBTOTAL(9,Fev!D47,Fev!D47,Mar!D47,Abr!D47,Mai!D47,Jun!D47,Jul!D47,Ago!D47,Set!D47,Out!D47,Nov!D47,Dez!D47)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="158"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="161"/>
-      <c r="L39" s="159"/>
-      <c r="M39" s="162">
+      <c r="I39" s="164"/>
+      <c r="J39" s="150"/>
+      <c r="K39" s="165"/>
+      <c r="L39" s="166"/>
+      <c r="M39" s="167">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="76"/>
       <c r="C40" s="65"/>
       <c r="D40" s="66">
         <f>SUBTOTAL(9,Fev!D48,Fev!D48,Mar!D48,Abr!D48,Mai!D48,Jun!D48,Jul!D48,Ago!D48,Set!D48,Out!D48,Nov!D48,Dez!D48)</f>
         <v>0</v>
       </c>
+      <c r="I40" s="178" t="s">
+        <v>115</v>
+      </c>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
+      <c r="L40" s="180">
+        <f>SUM(K30:K39)</f>
+        <v>2191.63</v>
+      </c>
+      <c r="M40" s="181"/>
     </row>
     <row r="41" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41"/>
@@ -9480,13 +9580,13 @@
       </c>
       <c r="D42" s="62">
         <f>SUBTOTAL(9,Fev!D50,Fev!D50,Mar!D50,Abr!D50,Mai!D50,Jun!D50,Jul!D50,Ago!D50,Set!D50,Out!D50,Nov!D50,Dez!D50)</f>
-        <v>37.5</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="68">
         <f>SUM(D42:D48)</f>
-        <v>624.98</v>
+        <v>694.88</v>
       </c>
       <c r="C43" s="63" t="s">
         <v>69</v>
@@ -9860,12 +9960,14 @@
       </c>
       <c r="D82" s="62">
         <f>SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
-        <v>1491.63</v>
+        <v>2191.63</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10037,19 +10139,19 @@
       </c>
     </row>
     <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="N9" s="49"/>
       <c r="P9" s="52" t="s">
         <v>65</v>
@@ -11048,10 +11150,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -11094,7 +11196,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -11165,19 +11267,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -12247,10 +12349,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -12293,7 +12395,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -12366,19 +12468,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -13458,10 +13560,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -13507,7 +13609,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -13587,19 +13689,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -14703,13 +14805,13 @@
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
     <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.140625" bestFit="1" customWidth="1"/>
@@ -14730,10 +14832,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
       <c r="N2" t="s">
         <v>208</v>
       </c>
@@ -14747,13 +14849,16 @@
         <v>4</v>
       </c>
       <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
+      <c r="D3" s="30">
+        <f>2500-O3-50</f>
+        <v>1650</v>
+      </c>
       <c r="E3" s="141" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1459.2399999999993</v>
+        <v>3109.2399999999993</v>
       </c>
       <c r="H3" s="116"/>
       <c r="I3" s="11" t="s">
@@ -14763,16 +14868,16 @@
         <v>166</v>
       </c>
       <c r="L3" s="118">
-        <f>(Abr!L3+220)</f>
-        <v>1563</v>
+        <f>(Abr!L3+320+840)</f>
+        <v>2503</v>
       </c>
       <c r="N3" s="116">
         <f>L3-O3</f>
-        <v>695.73</v>
+        <v>1703</v>
       </c>
       <c r="O3" s="116">
-        <f>(128.93+368.34+220+50+50+50)</f>
-        <v>867.27</v>
+        <f>300+500</f>
+        <v>800</v>
       </c>
       <c r="P3" s="116"/>
       <c r="Q3" s="116"/>
@@ -14791,14 +14896,14 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>1420.69</v>
+        <v>1840.5900000000001</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="L4" s="118">
         <v>0</v>
@@ -14843,22 +14948,22 @@
       </c>
       <c r="F6" s="36">
         <f>SUM(K11:K22)</f>
-        <v>81.83</v>
+        <v>498.83</v>
       </c>
       <c r="I6" s="14">
-        <v>46144</v>
+        <v>46155</v>
       </c>
       <c r="K6" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="L6" s="139"/>
+      <c r="L6" s="163">
+        <f>322-147</f>
+        <v>175</v>
+      </c>
       <c r="M6" t="s">
         <v>188</v>
       </c>
-      <c r="O6" s="146">
-        <f>Abr!L6</f>
-        <v>-50.939999999999969</v>
-      </c>
+      <c r="O6" s="146"/>
     </row>
     <row r="7" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -14874,25 +14979,25 @@
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>769.81999999999925</v>
       </c>
       <c r="P7" s="116"/>
     </row>
     <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -15025,10 +15130,16 @@
       <c r="F13" s="34">
         <v>1289.99</v>
       </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="13"/>
+      <c r="H13" s="19">
+        <v>46147</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="56"/>
+      <c r="K13" s="56">
+        <v>30</v>
+      </c>
       <c r="M13" s="72"/>
       <c r="N13" s="91"/>
       <c r="O13" s="82"/>
@@ -15050,10 +15161,17 @@
       <c r="F14" s="34">
         <v>44.7</v>
       </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="13"/>
+      <c r="H14" s="19">
+        <v>46150</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="56"/>
+      <c r="K14" s="56">
+        <f>2400*0.1</f>
+        <v>240</v>
+      </c>
       <c r="M14" s="72"/>
       <c r="N14" s="91"/>
       <c r="O14" s="82"/>
@@ -15075,21 +15193,39 @@
       <c r="F15" s="34">
         <v>48</v>
       </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="56"/>
+      <c r="H15" s="19">
+        <v>46153</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="56">
+        <v>147</v>
+      </c>
       <c r="M15" s="72"/>
       <c r="N15" s="91"/>
       <c r="O15" s="82"/>
       <c r="P15" s="56"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="22"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="34"/>
+      <c r="B16" s="22">
+        <v>46151</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="34">
+        <v>69.900000000000006</v>
+      </c>
       <c r="H16" s="19"/>
       <c r="I16" s="13"/>
       <c r="J16" s="1"/>
@@ -15100,11 +15236,19 @@
       <c r="P16" s="56"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="22"/>
-      <c r="C17" s="7"/>
+      <c r="B17" s="22">
+        <v>46151</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="34"/>
+      <c r="E17" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="34">
+        <v>350</v>
+      </c>
       <c r="H17" s="19"/>
       <c r="I17" s="13"/>
       <c r="J17" s="1"/>
@@ -15197,7 +15341,7 @@
       <c r="F23" s="34"/>
       <c r="K23" s="116">
         <f>SUM(K11:K22)</f>
-        <v>81.83</v>
+        <v>498.83</v>
       </c>
       <c r="M23" s="72"/>
       <c r="N23" s="91"/>
@@ -15239,10 +15383,6 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="34"/>
-      <c r="J27">
-        <f>(40.9/6)*3</f>
-        <v>20.45</v>
-      </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="22"/>
@@ -15316,7 +15456,7 @@
       </c>
       <c r="I36" s="64">
         <f t="shared" ref="I36:I45" si="1">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>6.8</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
@@ -15373,7 +15513,7 @@
       </c>
       <c r="I40" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
@@ -15412,7 +15552,7 @@
       </c>
       <c r="I42" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
@@ -15496,13 +15636,13 @@
       </c>
       <c r="D50" s="62">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="68">
         <f>SUM(D50:D56)</f>
-        <v>0</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C51" s="63" t="s">
         <v>69</v>
@@ -15843,7 +15983,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="62">
         <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>1289.99</v>
+        <v>1639.99</v>
       </c>
     </row>
   </sheetData>
@@ -15852,7 +15992,7 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="H9:K9"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D32">
       <formula1>INDIRECT(C11)</formula1>
     </dataValidation>
@@ -15860,7 +16000,7 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Modelo!$R$3:$R$14</xm:f>
@@ -15894,11 +16034,11 @@
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
     <col min="13" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15917,10 +16057,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -15933,7 +16073,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>769.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -15941,7 +16081,10 @@
       <c r="K3" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="118"/>
+      <c r="L3" s="118">
+        <f>Mai!L3</f>
+        <v>2503</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -15957,16 +16100,19 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="118"/>
+        <v>216</v>
+      </c>
+      <c r="L4" s="118">
+        <f>Mai!L4</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -15988,8 +16134,8 @@
         <v>179</v>
       </c>
       <c r="L5" s="118">
-        <f>SUM(P10:P25)</f>
-        <v>0</v>
+        <f>Mai!L5</f>
+        <v>156.5</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16020,31 +16166,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mai!F7</f>
-        <v>-43.280000000000726</v>
+        <v>769.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -16092,11 +16238,19 @@
       <c r="P10" s="55"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="33"/>
+      <c r="B11" s="22">
+        <v>46182</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="34">
+        <v>350</v>
+      </c>
       <c r="H11" s="18"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -16292,6 +16446,15 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="34"/>
+      <c r="H24" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" t="s">
+        <v>222</v>
+      </c>
+      <c r="J24" s="168">
+        <v>1000</v>
+      </c>
       <c r="M24" s="72"/>
       <c r="N24" s="91"/>
       <c r="O24" s="82"/>
@@ -16303,6 +16466,9 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="34"/>
+      <c r="I25" t="s">
+        <v>221</v>
+      </c>
       <c r="M25" s="65"/>
       <c r="N25" s="92"/>
       <c r="O25" s="83"/>
@@ -16314,6 +16480,15 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="34"/>
+      <c r="H26" t="s">
+        <v>226</v>
+      </c>
+      <c r="I26" t="s">
+        <v>212</v>
+      </c>
+      <c r="J26" s="169">
+        <v>700</v>
+      </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="22"/>
@@ -16321,6 +16496,15 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="34"/>
+      <c r="H27" t="s">
+        <v>218</v>
+      </c>
+      <c r="I27" t="s">
+        <v>213</v>
+      </c>
+      <c r="J27" s="169">
+        <v>112</v>
+      </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="22"/>
@@ -16328,6 +16512,15 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="34"/>
+      <c r="H28" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" t="s">
+        <v>214</v>
+      </c>
+      <c r="J28" s="169">
+        <v>499</v>
+      </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="22"/>
@@ -16335,6 +16528,16 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="34"/>
+      <c r="H29" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" s="169">
+        <v>40</v>
+      </c>
+      <c r="K29" s="116"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="22"/>
@@ -16342,6 +16545,15 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="34"/>
+      <c r="H30" t="s">
+        <v>223</v>
+      </c>
+      <c r="I30" t="s">
+        <v>215</v>
+      </c>
+      <c r="J30" s="168">
+        <v>350</v>
+      </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="22"/>
@@ -16349,6 +16561,15 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="34"/>
+      <c r="H31" t="s">
+        <v>217</v>
+      </c>
+      <c r="I31" t="s">
+        <v>225</v>
+      </c>
+      <c r="J31" s="168">
+        <v>150</v>
+      </c>
     </row>
     <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="23"/>
@@ -16356,6 +16577,10 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="35"/>
+      <c r="J32" s="146">
+        <f>SUM(J24:J31)</f>
+        <v>2851</v>
+      </c>
     </row>
     <row r="34" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -16921,7 +17146,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="62">
         <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -16930,7 +17155,7 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="H9:K9"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D32">
       <formula1>INDIRECT(C11)</formula1>
     </dataValidation>
@@ -16938,7 +17163,7 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Modelo!$R$3:$R$14</xm:f>
@@ -16995,10 +17220,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -17011,7 +17236,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -17039,7 +17264,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -17098,31 +17323,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jun!F7</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -18073,10 +18298,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -18089,7 +18314,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -18119,7 +18344,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -18178,31 +18403,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jul!F7</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -19153,10 +19378,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -19169,7 +19394,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -19197,7 +19422,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -19256,31 +19481,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Ago!F7</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-43.280000000000726</v>
+        <v>419.81999999999925</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="H9" s="169" t="s">
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="172"/>
+      <c r="H9" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="839" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="839" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Jan" sheetId="1" r:id="rId1"/>
@@ -17,8 +17,8 @@
     <sheet name="Mar" sheetId="11" r:id="rId3"/>
     <sheet name="Abr" sheetId="12" r:id="rId4"/>
     <sheet name="Mai" sheetId="13" r:id="rId5"/>
-    <sheet name="Jun" sheetId="14" r:id="rId6"/>
-    <sheet name="Jul" sheetId="4" r:id="rId7"/>
+    <sheet name="Jul" sheetId="4" r:id="rId6"/>
+    <sheet name="Jun" sheetId="14" r:id="rId7"/>
     <sheet name="Ago" sheetId="5" r:id="rId8"/>
     <sheet name="Set" sheetId="6" r:id="rId9"/>
     <sheet name="Out" sheetId="7" r:id="rId10"/>
@@ -26,7 +26,7 @@
     <sheet name="Dez" sheetId="9" r:id="rId12"/>
     <sheet name="Anual" sheetId="3" r:id="rId13"/>
     <sheet name="Gastos Fixos anual" sheetId="16" r:id="rId14"/>
-    <sheet name="Modelo" sheetId="2" r:id="rId15"/>
+    <sheet name="Modelo" sheetId="2" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="Alimentação">Modelo!$N$4:$N$8</definedName>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="249">
   <si>
     <t>JAN</t>
   </si>
@@ -767,6 +767,72 @@
   </si>
   <si>
     <t>amazon OU shoope</t>
+  </si>
+  <si>
+    <t>pc - fonte e cooler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cooler </t>
+  </si>
+  <si>
+    <t>amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fonte </t>
+  </si>
+  <si>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>ssd</t>
+  </si>
+  <si>
+    <t>placa de video</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Mouse pad</t>
+  </si>
+  <si>
+    <t>pasta termica</t>
+  </si>
+  <si>
+    <t>aliespress</t>
+  </si>
+  <si>
+    <t>teclado</t>
+  </si>
+  <si>
+    <t>mercado livre</t>
+  </si>
+  <si>
+    <t>magalu</t>
+  </si>
+  <si>
+    <t>pc - mouse e mouse pad</t>
+  </si>
+  <si>
+    <t>pen drive</t>
+  </si>
+  <si>
+    <t>facul</t>
+  </si>
+  <si>
+    <t>pc - teclado</t>
+  </si>
+  <si>
+    <t>pc - monitor</t>
+  </si>
+  <si>
+    <t>perifericos</t>
+  </si>
+  <si>
+    <t>pc - bruto</t>
   </si>
 </sst>
 </file>
@@ -777,7 +843,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,6 +929,12 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1665,7 +1737,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2004,19 +2076,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="20" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="21" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="23" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2026,9 +2086,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="25" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2044,21 +2101,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="25" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="25" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2095,6 +2143,27 @@
     </xf>
     <xf numFmtId="44" fontId="11" fillId="26" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="17" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2781,7 +2850,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>3945.2699999999995</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3770,10 +3839,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -3822,7 +3891,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -3890,19 +3959,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>135</v>
       </c>
@@ -5009,10 +5078,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -5025,7 +5094,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -5053,7 +5122,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -5112,31 +5181,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Set!F7</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -6087,10 +6156,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -6103,7 +6172,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -6131,7 +6200,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -6190,31 +6259,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Out!F7</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -7170,10 +7239,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
       <c r="N2"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7187,7 +7256,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -7216,7 +7285,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -7278,14 +7347,14 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Nov!F7</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="N7"/>
     </row>
@@ -7293,19 +7362,19 @@
       <c r="N8"/>
     </row>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -8311,39 +8380,39 @@
       </c>
       <c r="G3" s="124">
         <f>Mai!$F$3</f>
-        <v>3109.2399999999993</v>
+        <v>1879.2399999999993</v>
       </c>
       <c r="H3" s="124">
         <f>Jun!$F$3</f>
-        <v>769.81999999999925</v>
+        <v>-2224.5100000000011</v>
       </c>
       <c r="I3" s="124">
         <f>Jul!$F$3</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="J3" s="124">
         <f>Ago!$F$3</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="K3" s="124">
         <f>Set!$F$3</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="L3" s="124">
         <f>Out!$F$3</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="M3" s="124">
         <f>Nov!$F$3</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="N3" s="125">
         <f>Dez!$F$3</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="O3" s="125">
         <f>SUM(C3:N3)</f>
-        <v>15685.909999999996</v>
+        <v>-6504.4000000000106</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8368,7 +8437,7 @@
       </c>
       <c r="G4" s="126">
         <f>Mai!$F$4</f>
-        <v>1840.5900000000001</v>
+        <v>3687.9200000000005</v>
       </c>
       <c r="H4" s="126">
         <f>Jun!$F$4</f>
@@ -8400,7 +8469,7 @@
       </c>
       <c r="O4" s="127">
         <f t="shared" ref="O4:O10" si="0">SUM(C4:N4)</f>
-        <v>5246.93</v>
+        <v>7094.26</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8596,7 +8665,7 @@
       </c>
       <c r="G8" s="132">
         <f t="shared" si="1"/>
-        <v>2339.42</v>
+        <v>4186.7500000000009</v>
       </c>
       <c r="H8" s="132">
         <f t="shared" si="1"/>
@@ -8628,7 +8697,7 @@
       </c>
       <c r="O8" s="133">
         <f t="shared" si="0"/>
-        <v>7396.25</v>
+        <v>9243.5800000000017</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8653,39 +8722,39 @@
       </c>
       <c r="G9" s="134">
         <f t="shared" si="2"/>
-        <v>769.81999999999925</v>
+        <v>-2307.5100000000016</v>
       </c>
       <c r="H9" s="134">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="I9" s="134">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="J9" s="134">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="K9" s="134">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="L9" s="134">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="M9" s="134">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="N9" s="135">
         <f t="shared" si="2"/>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="O9" s="135">
         <f>N9</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -8746,7 +8815,12 @@
       </c>
     </row>
     <row r="12" spans="2:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="43">
+        <f>12*25.82</f>
+        <v>309.84000000000003</v>
+      </c>
+    </row>
     <row r="14" spans="2:15" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="47" t="s">
@@ -8928,7 +9002,7 @@
       </c>
       <c r="G18" s="101">
         <f>Mai!$B$51</f>
-        <v>69.900000000000006</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="H18" s="102">
         <f>Jun!$B$51</f>
@@ -8960,7 +9034,7 @@
       </c>
       <c r="O18" s="109">
         <f t="shared" si="3"/>
-        <v>562.59</v>
+        <v>569.59</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
@@ -9138,19 +9212,55 @@
       <c r="B22" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="151"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="151"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="151"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="151"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="151"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="152"/>
-      <c r="O22" s="153"/>
+      <c r="C22" s="101">
+        <f>Jan!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="101">
+        <f>Fev!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="101">
+        <f>Mar!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="101">
+        <f>Abr!$D$90</f>
+        <v>201.64</v>
+      </c>
+      <c r="G22" s="101">
+        <f>Mai!$D$90</f>
+        <v>3393.6299999999997</v>
+      </c>
+      <c r="H22" s="101">
+        <f>Jun!$D$90</f>
+        <v>350</v>
+      </c>
+      <c r="I22" s="101">
+        <f>Jul!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="101">
+        <f>Ago!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="101">
+        <f>Set!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="101">
+        <f>Out!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="101">
+        <f>Nov!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="101">
+        <f>Dez!$D$90</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="150"/>
     </row>
     <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="104" t="s">
@@ -9243,15 +9353,15 @@
         <f>SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
         <v>30</v>
       </c>
-      <c r="I28" s="175" t="s">
+      <c r="I28" s="167" t="s">
         <v>194</v>
       </c>
-      <c r="J28" s="176"/>
-      <c r="K28" s="176"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="155">
-        <f>SUM(L30:L39)-SUM(K30:K39)</f>
-        <v>610.05999999999995</v>
+      <c r="J28" s="168"/>
+      <c r="K28" s="168"/>
+      <c r="L28" s="169"/>
+      <c r="M28" s="151">
+        <f>SUM(L30:L43)-SUM(K30:K43)</f>
+        <v>3215.99</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -9270,19 +9380,19 @@
         <f>SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
         <v>330.1</v>
       </c>
-      <c r="I29" s="160" t="s">
+      <c r="I29" s="155" t="s">
         <v>195</v>
       </c>
-      <c r="J29" s="161" t="s">
+      <c r="J29" s="156" t="s">
         <v>201</v>
       </c>
-      <c r="K29" s="161" t="s">
+      <c r="K29" s="156" t="s">
         <v>196</v>
       </c>
-      <c r="L29" s="161" t="s">
+      <c r="L29" s="156" t="s">
         <v>197</v>
       </c>
-      <c r="M29" s="162" t="s">
+      <c r="M29" s="157" t="s">
         <v>198</v>
       </c>
     </row>
@@ -9302,20 +9412,20 @@
         <f>SUBTOTAL(9,Jan!I37,Fev!I37,Mar!I37,Abr!I37,Mai!I37,Jun!I37,Jul!I37,Ago!I37,Set!I37,Out!I37,Nov!I37,Dez!I37)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="154" t="s">
+      <c r="I30" s="175" t="s">
         <v>200</v>
       </c>
-      <c r="J30" s="101" t="s">
+      <c r="J30" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="158">
+      <c r="K30" s="176">
         <v>201.64</v>
       </c>
-      <c r="L30" s="156">
+      <c r="L30" s="176">
         <f>200.05+10+10+64</f>
         <v>284.05</v>
       </c>
-      <c r="M30" s="159">
+      <c r="M30" s="154">
         <f>L30-K30</f>
         <v>82.410000000000025</v>
       </c>
@@ -9334,19 +9444,19 @@
         <f>SUBTOTAL(9,Jan!I38,Fev!I38,Mar!I38,Abr!I38,Mai!I38,Jun!I38,Jul!I38,Ago!I38,Set!I38,Out!I38,Nov!I38,Dez!I38)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="157" t="s">
+      <c r="I31" s="177" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="101" t="s">
+      <c r="J31" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="K31" s="158">
+      <c r="K31" s="176">
         <v>1289.99</v>
       </c>
-      <c r="L31" s="156">
+      <c r="L31" s="176">
         <v>1517.64</v>
       </c>
-      <c r="M31" s="159">
+      <c r="M31" s="154">
         <f t="shared" ref="M31:M39" si="4">L31-K31</f>
         <v>227.65000000000009</v>
       </c>
@@ -9362,19 +9472,19 @@
         <f>SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
         <v>302.22000000000003</v>
       </c>
-      <c r="I32" s="157" t="s">
+      <c r="I32" s="177" t="s">
         <v>204</v>
       </c>
-      <c r="J32" s="101" t="s">
+      <c r="J32" s="176" t="s">
         <v>205</v>
       </c>
-      <c r="K32" s="158">
+      <c r="K32" s="176">
         <v>700</v>
       </c>
-      <c r="L32" s="156">
+      <c r="L32" s="176">
         <v>1000</v>
       </c>
-      <c r="M32" s="159">
+      <c r="M32" s="154">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
@@ -9397,13 +9507,24 @@
         <f>SUBTOTAL(9,Jan!I40,Fev!I40,Mar!I40,Abr!I40,Mai!I40,Jun!I40,Jul!I40,Ago!I40,Set!I40,Out!I40,Nov!I40,Dez!I40)</f>
         <v>500</v>
       </c>
-      <c r="I33" s="157"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="159">
+      <c r="H33" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="I33" s="177" t="s">
+        <v>228</v>
+      </c>
+      <c r="J33" s="176" t="s">
+        <v>229</v>
+      </c>
+      <c r="K33" s="176">
+        <v>128</v>
+      </c>
+      <c r="L33" s="176">
+        <v>176</v>
+      </c>
+      <c r="M33" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9425,13 +9546,25 @@
         <f>SUBTOTAL(9,Jan!I41,Fev!I41,Mar!I41,Abr!I41,Mai!I41,Jun!I41,Jul!I41,Ago!I41,Set!I41,Out!I41,Nov!I41,Dez!I41)</f>
         <v>40</v>
       </c>
-      <c r="I34" s="157"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="158"/>
-      <c r="L34" s="156"/>
-      <c r="M34" s="159">
+      <c r="H34" s="43">
+        <f>SUM(K30:K37)</f>
+        <v>7682.51</v>
+      </c>
+      <c r="I34" s="177" t="s">
+        <v>230</v>
+      </c>
+      <c r="J34" s="176" t="s">
+        <v>229</v>
+      </c>
+      <c r="K34" s="176">
+        <v>320.74</v>
+      </c>
+      <c r="L34" s="176">
+        <v>385</v>
+      </c>
+      <c r="M34" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>64.259999999999991</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
@@ -9450,13 +9583,21 @@
         <f>SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
         <v>877</v>
       </c>
-      <c r="I35" s="157"/>
-      <c r="J35" s="101"/>
-      <c r="K35" s="158"/>
-      <c r="L35" s="156"/>
-      <c r="M35" s="159">
+      <c r="I35" s="153" t="s">
+        <v>231</v>
+      </c>
+      <c r="J35" s="101" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" s="174">
+        <v>1715.14</v>
+      </c>
+      <c r="L35" s="152">
+        <v>2017.8</v>
+      </c>
+      <c r="M35" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>302.65999999999985</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
@@ -9475,13 +9616,21 @@
         <f>SUBTOTAL(9,Jan!I43,Fev!I43,Mar!I43,Abr!I43,Mai!I43,Jun!I43,Jul!I43,Ago!I43,Set!I43,Out!I43,Nov!I43,Dez!I43)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="157"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="158"/>
-      <c r="L36" s="156"/>
-      <c r="M36" s="159">
+      <c r="I36" s="153" t="s">
+        <v>232</v>
+      </c>
+      <c r="J36" s="101" t="s">
+        <v>240</v>
+      </c>
+      <c r="K36" s="174">
+        <v>949</v>
+      </c>
+      <c r="L36" s="152">
+        <v>1045</v>
+      </c>
+      <c r="M36" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
@@ -9497,16 +9646,24 @@
         <v>100</v>
       </c>
       <c r="G37" s="64">
-        <f>SUBTOTAL(9,Jan!I44,Fev!I44,Mar!I44,Abr!I44,Mai!I44,Jun!I44,Jul!I44,Ago!I44,Set!I44,Out!I44,Nov!I44,Dez!I44)</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="157"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="158"/>
-      <c r="L37" s="156"/>
-      <c r="M37" s="159">
+        <f>SUBTOTAL(9,C22:N22)</f>
+        <v>3945.2699999999995</v>
+      </c>
+      <c r="I37" s="153" t="s">
+        <v>233</v>
+      </c>
+      <c r="J37" s="101" t="s">
+        <v>240</v>
+      </c>
+      <c r="K37" s="174">
+        <v>2378</v>
+      </c>
+      <c r="L37" s="152">
+        <v>3669</v>
+      </c>
+      <c r="M37" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9523,32 +9680,48 @@
         <f>SUBTOTAL(9,Jan!I45,Fev!I45,Mar!I45,Abr!I45,Mai!I45,Jun!I45,Jul!I45,Ago!I45,Set!I45,Out!I45,Nov!I45,Dez!I45)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="157"/>
-      <c r="J38" s="101"/>
-      <c r="K38" s="158"/>
-      <c r="L38" s="156"/>
-      <c r="M38" s="159">
+      <c r="I38" s="153" t="s">
+        <v>243</v>
+      </c>
+      <c r="J38" s="101" t="s">
+        <v>240</v>
+      </c>
+      <c r="K38" s="174">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="L38" s="152">
+        <v>93.24</v>
+      </c>
+      <c r="M38" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>14.339999999999989</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39"/>
       <c r="C39" s="69"/>
       <c r="D39" s="70">
         <f>SUBTOTAL(9,Fev!D47,Fev!D47,Mar!D47,Abr!D47,Mai!D47,Jun!D47,Jul!D47,Ago!D47,Set!D47,Out!D47,Nov!D47,Dez!D47)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="164"/>
-      <c r="J39" s="150"/>
-      <c r="K39" s="165"/>
-      <c r="L39" s="166"/>
-      <c r="M39" s="167">
+      <c r="I39" s="177" t="s">
+        <v>234</v>
+      </c>
+      <c r="J39" s="176" t="s">
+        <v>203</v>
+      </c>
+      <c r="K39" s="176">
+        <v>630</v>
+      </c>
+      <c r="L39" s="176">
+        <v>741</v>
+      </c>
+      <c r="M39" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="76"/>
       <c r="C40" s="65"/>
       <c r="D40" s="66">
@@ -9556,20 +9729,42 @@
         <v>0</v>
       </c>
       <c r="I40" s="178" t="s">
-        <v>115</v>
-      </c>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
-      <c r="L40" s="180">
-        <f>SUM(K30:K39)</f>
-        <v>2191.63</v>
-      </c>
-      <c r="M40" s="181"/>
+        <v>239</v>
+      </c>
+      <c r="J40" s="176" t="s">
+        <v>238</v>
+      </c>
+      <c r="K40" s="176">
+        <v>394</v>
+      </c>
+      <c r="L40" s="176">
+        <v>765</v>
+      </c>
+      <c r="M40" s="154">
+        <f t="shared" ref="M40" si="5">L40-K40</f>
+        <v>371</v>
+      </c>
     </row>
     <row r="41" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
+      <c r="I41" s="153" t="s">
+        <v>237</v>
+      </c>
+      <c r="J41" s="101" t="s">
+        <v>240</v>
+      </c>
+      <c r="K41" s="174">
+        <v>59.9</v>
+      </c>
+      <c r="L41" s="152">
+        <v>103.9</v>
+      </c>
+      <c r="M41" s="154">
+        <f t="shared" ref="M41:M42" si="6">L41-K41</f>
+        <v>44.000000000000007</v>
+      </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="67" t="s">
@@ -9582,11 +9777,30 @@
         <f>SUBTOTAL(9,Fev!D50,Fev!D50,Mar!D50,Abr!D50,Mai!D50,Jun!D50,Jul!D50,Ago!D50,Set!D50,Out!D50,Nov!D50,Dez!D50)</f>
         <v>107.4</v>
       </c>
+      <c r="H42" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="I42" s="177" t="s">
+        <v>235</v>
+      </c>
+      <c r="J42" s="176" t="s">
+        <v>238</v>
+      </c>
+      <c r="K42" s="176">
+        <v>175</v>
+      </c>
+      <c r="L42" s="176">
+        <v>373.58</v>
+      </c>
+      <c r="M42" s="154">
+        <f t="shared" si="6"/>
+        <v>198.57999999999998</v>
+      </c>
     </row>
     <row r="43" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="68">
         <f>SUM(D42:D48)</f>
-        <v>694.88</v>
+        <v>701.88</v>
       </c>
       <c r="C43" s="63" t="s">
         <v>69</v>
@@ -9595,8 +9809,28 @@
         <f>SUBTOTAL(9,Fev!D51,Fev!D51,Mar!D51,Abr!D51,Mai!D51,Jun!D51,Jul!D51,Ago!D51,Set!D51,Out!D51,Nov!D51,Dez!D51)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="H43" s="43">
+        <f>SUM(K38:K43)</f>
+        <v>1444.5600000000002</v>
+      </c>
+      <c r="I43" s="179" t="s">
+        <v>236</v>
+      </c>
+      <c r="J43" s="180" t="s">
+        <v>238</v>
+      </c>
+      <c r="K43" s="180">
+        <v>106.76</v>
+      </c>
+      <c r="L43" s="180">
+        <v>171.85</v>
+      </c>
+      <c r="M43" s="161">
+        <f>L43-K43</f>
+        <v>65.089999999999989</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44"/>
       <c r="C44" s="63" t="s">
         <v>70</v>
@@ -9606,15 +9840,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45"/>
       <c r="C45" s="63" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="64">
         <f>SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
-        <v>135</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="I45" s="170" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" s="171"/>
+      <c r="K45" s="171"/>
+      <c r="L45" s="172">
+        <f>SUM(K30:K43)</f>
+        <v>9127.07</v>
+      </c>
+      <c r="M45" s="173"/>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46"/>
@@ -9960,14 +10204,14 @@
       </c>
       <c r="D82" s="62">
         <f>SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
-        <v>2191.63</v>
+        <v>3945.2699999999995</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="L45:M45"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10139,19 +10383,19 @@
       </c>
     </row>
     <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="N9" s="49"/>
       <c r="P9" s="52" t="s">
         <v>65</v>
@@ -11150,10 +11394,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -11196,7 +11440,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -11267,19 +11511,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -12349,10 +12593,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -12395,7 +12639,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -12468,19 +12712,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -13560,10 +13804,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -13609,7 +13853,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -13689,19 +13933,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -14832,10 +15076,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
       <c r="N2" t="s">
         <v>208</v>
       </c>
@@ -14851,14 +15095,14 @@
       <c r="C3" s="29"/>
       <c r="D3" s="30">
         <f>2500-O3-50</f>
-        <v>1650</v>
+        <v>420</v>
       </c>
       <c r="E3" s="141" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>3109.2399999999993</v>
+        <v>1879.2399999999993</v>
       </c>
       <c r="H3" s="116"/>
       <c r="I3" s="11" t="s">
@@ -14873,11 +15117,11 @@
       </c>
       <c r="N3" s="116">
         <f>L3-O3</f>
-        <v>1703</v>
+        <v>473</v>
       </c>
       <c r="O3" s="116">
-        <f>300+500</f>
-        <v>800</v>
+        <f>300+500+150+400+50+630</f>
+        <v>2030</v>
       </c>
       <c r="P3" s="116"/>
       <c r="Q3" s="116"/>
@@ -14896,11 +15140,11 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>1840.5900000000001</v>
+        <v>3687.9200000000005</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>209</v>
@@ -14951,19 +15195,22 @@
         <v>498.83</v>
       </c>
       <c r="I6" s="14">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="K6" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="L6" s="163">
-        <f>322-147</f>
-        <v>175</v>
+      <c r="L6" s="158">
+        <f>322-147-F20-F21</f>
+        <v>83</v>
       </c>
       <c r="M6" t="s">
         <v>188</v>
       </c>
-      <c r="O6" s="146"/>
+      <c r="O6" s="146">
+        <f>O3+L6</f>
+        <v>2113</v>
+      </c>
     </row>
     <row r="7" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -14978,26 +15225,27 @@
         <v>108</v>
       </c>
       <c r="F7" s="39">
-        <f>F3-F4-F6</f>
-        <v>769.81999999999925</v>
-      </c>
+        <f>F3-F4-F6+L6</f>
+        <v>-2224.5100000000011</v>
+      </c>
+      <c r="L7" s="116"/>
       <c r="P7" s="116"/>
     </row>
     <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -15066,7 +15314,8 @@
         <v>118</v>
       </c>
       <c r="F11" s="33">
-        <v>10</v>
+        <f>10+1.69</f>
+        <v>11.69</v>
       </c>
       <c r="H11" s="18">
         <v>46144</v>
@@ -15259,11 +15508,19 @@
       <c r="P17" s="56"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="22"/>
-      <c r="C18" s="7"/>
+      <c r="B18" s="22">
+        <v>46125</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="34"/>
+      <c r="E18" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" s="34">
+        <v>448.74</v>
+      </c>
       <c r="H18" s="19"/>
       <c r="I18" s="13"/>
       <c r="J18" s="1"/>
@@ -15274,11 +15531,19 @@
       <c r="P18" s="56"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="22"/>
-      <c r="C19" s="7"/>
+      <c r="B19" s="22">
+        <v>46157</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="34"/>
+      <c r="E19" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" s="34">
+        <v>281.76</v>
+      </c>
       <c r="H19" s="19"/>
       <c r="I19" s="13"/>
       <c r="J19" s="1"/>
@@ -15289,11 +15554,21 @@
       <c r="P19" s="56"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="22"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="34"/>
+      <c r="B20" s="22">
+        <v>46163</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="34">
+        <v>7</v>
+      </c>
       <c r="H20" s="19"/>
       <c r="I20" s="13"/>
       <c r="J20" s="1"/>
@@ -15304,11 +15579,19 @@
       <c r="P20" s="56"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="22"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="B21" s="22">
+        <v>46163</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="E21" s="7"/>
-      <c r="F21" s="34"/>
+      <c r="F21" s="34">
+        <v>85</v>
+      </c>
       <c r="H21" s="19"/>
       <c r="I21" s="13"/>
       <c r="J21" s="1"/>
@@ -15319,11 +15602,19 @@
       <c r="P21" s="56"/>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="22"/>
-      <c r="C22" s="7"/>
+      <c r="B22" s="22">
+        <v>46163</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="34"/>
+      <c r="E22" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F22" s="34">
+        <v>394.14</v>
+      </c>
       <c r="H22" s="20"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -15334,15 +15625,20 @@
       <c r="P22" s="56"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="22"/>
-      <c r="C23" s="7"/>
+      <c r="B23" s="22">
+        <v>46164</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="34"/>
-      <c r="K23" s="116">
-        <f>SUM(K11:K22)</f>
-        <v>498.83</v>
-      </c>
+      <c r="E23" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F23" s="34">
+        <v>629</v>
+      </c>
+      <c r="K23" s="116"/>
       <c r="M23" s="72"/>
       <c r="N23" s="91"/>
       <c r="O23" s="82"/>
@@ -15642,7 +15938,7 @@
     <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="68">
         <f>SUM(D50:D56)</f>
-        <v>69.900000000000006</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="C51" s="63" t="s">
         <v>69</v>
@@ -15667,7 +15963,7 @@
       </c>
       <c r="D53" s="64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -15983,7 +16279,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="62">
         <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>1639.99</v>
+        <v>3393.6299999999997</v>
       </c>
     </row>
   </sheetData>
@@ -16021,6 +16317,1084 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Plan7">
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:P90"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="32"/>
+      <c r="F2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="141" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="38">
+        <f>SUM(D3,D5,D6,D7,D4)</f>
+        <v>-2574.5100000000011</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="117" t="s">
+        <v>166</v>
+      </c>
+      <c r="L3" s="118"/>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="26">
+        <f>SUM(P10:P25)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="142" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="37">
+        <f>SUM(F11:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="15">
+        <f ca="1">TODAY()</f>
+        <v>46164</v>
+      </c>
+      <c r="K4" s="117" t="s">
+        <v>167</v>
+      </c>
+      <c r="L4" s="118"/>
+    </row>
+    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="143" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="93">
+        <f>D4</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="117" t="s">
+        <v>179</v>
+      </c>
+      <c r="L5" s="118">
+        <f>SUM(P10:P25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="144" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="36">
+        <f>SUM(K11:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
+        <v>45847</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>171</v>
+      </c>
+      <c r="L6" s="139"/>
+    </row>
+    <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="28">
+        <f>Jun!F7</f>
+        <v>-2574.5100000000011</v>
+      </c>
+      <c r="E7" s="145" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="39">
+        <f>F3-F4-F6</f>
+        <v>-2574.5100000000011</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="162" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+      <c r="M9" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="N9" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="O9" s="88" t="s">
+        <v>112</v>
+      </c>
+      <c r="P9" s="89" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M10" s="84"/>
+      <c r="N10" s="90"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="55"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="21"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="33"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="55"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="56"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="22"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="34"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="56"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="56"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="22"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="34"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="56"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="56"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="22"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="34"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="56"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="56"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="22"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="34"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="56"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="56"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" s="22"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="34"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="56"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="56"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="22"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="34"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="56"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="82"/>
+      <c r="P17" s="56"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="22"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="34"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="56"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="56"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="22"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="34"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="56"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="56"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="22"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="34"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="56"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="56"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="22"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="34"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="56"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="56"/>
+    </row>
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="22"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="34"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="57"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="82"/>
+      <c r="P22" s="56"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="22"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="34"/>
+      <c r="K23" s="116">
+        <f>SUM(K11:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="72"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="56"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" s="22"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="34"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="56"/>
+    </row>
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="22"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="34"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="92"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="57"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="22"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="34"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="22"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="34"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B28" s="22"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="34"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="22"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="22"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="34"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="22"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="34"/>
+    </row>
+    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="23"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="35"/>
+    </row>
+    <row r="34" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="62">
+        <f>SUMIF($D$11:$D$32,C35,$F$11:$F$32)</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="I35" s="62">
+        <f>SUMIF($I$11:$I$22,H35,$K$11:$K$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="68">
+        <f>SUM(D35:D39)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="64">
+        <f t="shared" ref="D36:D88" si="0">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="I36" s="64">
+        <f t="shared" ref="I36:I45" si="1">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C37" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="I37" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C38" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="I38" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="71"/>
+      <c r="D39" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="I39" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="49"/>
+      <c r="D40" s="58"/>
+      <c r="H40" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="I40" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="I41" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="68">
+        <f>SUBTOTAL(9,D41:D48)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="I42" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C43" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C44" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I44" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="75"/>
+      <c r="I45" s="66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C46" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C47" s="69"/>
+      <c r="D47" s="70">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="71"/>
+      <c r="D48" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D49" s="58"/>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="68">
+        <f>SUM(D50:D56)</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C52" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C54" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C55" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="65"/>
+      <c r="D56" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="58"/>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="68">
+        <f>SUM(D58:D64)</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C60" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C61" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C62" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="D62" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C63" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="65"/>
+      <c r="D64" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D65" s="58"/>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="D66" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="68">
+        <f>SUM(D66:D72)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C68" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C69" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C70" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C71" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="65"/>
+      <c r="D72" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="58"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="C74" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="D74" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="68">
+        <f>SUM(D74:D80)</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C76" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D76" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C77" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C78" s="63"/>
+      <c r="D78" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C79" s="63"/>
+      <c r="D79" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="65"/>
+      <c r="D80" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="58"/>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="68">
+        <f>SUM(D82:D88)</f>
+        <v>0</v>
+      </c>
+      <c r="C83" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="D83" s="64">
+        <f>SUMIF($D$11:$D$32,C83,$F$11:$F$32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C84" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C85" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C86" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C87" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="65"/>
+      <c r="D88" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B90" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="61"/>
+      <c r="D90" s="62">
+        <f>SUMIF(C11:C32,B90,F11:F32)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="H9:K9"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D32">
+      <formula1>INDIRECT(C11)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Modelo!$R$3:$R$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>I11:I22</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Modelo!$P$3:$P$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>C11:C32</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Plan6">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
@@ -16057,10 +17431,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -16073,7 +17447,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>769.81999999999925</v>
+        <v>-2224.5100000000011</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -16104,7 +17478,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>216</v>
@@ -16166,31 +17540,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Mai!F7</f>
-        <v>769.81999999999925</v>
+        <v>-2224.5100000000011</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -16452,7 +17826,7 @@
       <c r="I24" t="s">
         <v>222</v>
       </c>
-      <c r="J24" s="168">
+      <c r="J24" s="159">
         <v>1000</v>
       </c>
       <c r="M24" s="72"/>
@@ -16486,7 +17860,7 @@
       <c r="I26" t="s">
         <v>212</v>
       </c>
-      <c r="J26" s="169">
+      <c r="J26" s="160">
         <v>700</v>
       </c>
     </row>
@@ -16502,7 +17876,7 @@
       <c r="I27" t="s">
         <v>213</v>
       </c>
-      <c r="J27" s="169">
+      <c r="J27" s="160">
         <v>112</v>
       </c>
     </row>
@@ -16518,7 +17892,7 @@
       <c r="I28" t="s">
         <v>214</v>
       </c>
-      <c r="J28" s="169">
+      <c r="J28" s="160">
         <v>499</v>
       </c>
     </row>
@@ -16534,7 +17908,7 @@
       <c r="I29" t="s">
         <v>220</v>
       </c>
-      <c r="J29" s="169">
+      <c r="J29" s="160">
         <v>40</v>
       </c>
       <c r="K29" s="116"/>
@@ -16551,7 +17925,7 @@
       <c r="I30" t="s">
         <v>215</v>
       </c>
-      <c r="J30" s="168">
+      <c r="J30" s="159">
         <v>350</v>
       </c>
     </row>
@@ -16567,7 +17941,7 @@
       <c r="I31" t="s">
         <v>225</v>
       </c>
-      <c r="J31" s="168">
+      <c r="J31" s="159">
         <v>150</v>
       </c>
     </row>
@@ -17164,1084 +18538,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Modelo!$R$3:$R$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>I11:I22</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Modelo!$P$3:$P$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>C11:C32</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Plan7">
-    <tabColor theme="4" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="B1:P90"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="141" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="38">
-        <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>419.81999999999925</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="117" t="s">
-        <v>166</v>
-      </c>
-      <c r="L3" s="118"/>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="26">
-        <f>SUM(P10:P25)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="142" t="s">
-        <v>182</v>
-      </c>
-      <c r="F4" s="37">
-        <f>SUM(F11:F32)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="15">
-        <f ca="1">TODAY()</f>
-        <v>46155</v>
-      </c>
-      <c r="K4" s="117" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="118"/>
-    </row>
-    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="143" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" s="93">
-        <f>D4</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="117" t="s">
-        <v>179</v>
-      </c>
-      <c r="L5" s="118">
-        <f>SUM(P10:P25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="144" t="s">
-        <v>184</v>
-      </c>
-      <c r="F6" s="36">
-        <f>SUM(K11:K22)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="14">
-        <v>45847</v>
-      </c>
-      <c r="K6" s="138" t="s">
-        <v>171</v>
-      </c>
-      <c r="L6" s="139"/>
-    </row>
-    <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="28">
-        <f>Jun!F7</f>
-        <v>419.81999999999925</v>
-      </c>
-      <c r="E7" s="145" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="39">
-        <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
-      <c r="M9" s="86" t="s">
-        <v>110</v>
-      </c>
-      <c r="N9" s="87" t="s">
-        <v>111</v>
-      </c>
-      <c r="O9" s="88" t="s">
-        <v>112</v>
-      </c>
-      <c r="P9" s="89" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M10" s="84"/>
-      <c r="N10" s="90"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="55"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="33"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="55"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="82"/>
-      <c r="P11" s="56"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="22"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="34"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="56"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="56"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="22"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="34"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="56"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="56"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="22"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="34"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="56"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="82"/>
-      <c r="P14" s="56"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="34"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="56"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="56"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="22"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="34"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="56"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="56"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="22"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="34"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="56"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="82"/>
-      <c r="P17" s="56"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="22"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="34"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="56"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="82"/>
-      <c r="P18" s="56"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="22"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="34"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="56"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="56"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="22"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="34"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="56"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="56"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="22"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="34"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="56"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="82"/>
-      <c r="P21" s="56"/>
-    </row>
-    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="22"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="34"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="57"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="56"/>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="22"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="34"/>
-      <c r="K23" s="116">
-        <f>SUM(K11:K22)</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="72"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="56"/>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="22"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="34"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="56"/>
-    </row>
-    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="22"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="34"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="92"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="57"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B26" s="22"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="34"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="34"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="22"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="34"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="22"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="34"/>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="22"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="34"/>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="22"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="34"/>
-    </row>
-    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="23"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="35"/>
-    </row>
-    <row r="34" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" s="62">
-        <f>SUMIF($D$11:$D$32,C35,$F$11:$F$32)</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="I35" s="62">
-        <f>SUMIF($I$11:$I$22,H35,$K$11:$K$22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="68">
-        <f>SUM(D35:D39)</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="64">
-        <f t="shared" ref="D36:D88" si="0">SUMIF($D$11:$D$32,C36,$F$11:$F$32)</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="74" t="s">
-        <v>93</v>
-      </c>
-      <c r="I36" s="64">
-        <f t="shared" ref="I36:I45" si="1">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C37" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="I37" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C38" s="63" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="I38" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="71"/>
-      <c r="D39" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="I39" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="49"/>
-      <c r="D40" s="58"/>
-      <c r="H40" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I40" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="I41" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="68">
-        <f>SUBTOTAL(9,D41:D48)</f>
-        <v>0</v>
-      </c>
-      <c r="C42" s="63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="I42" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C43" s="63" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="I43" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C44" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="D44" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="I44" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="75"/>
-      <c r="I45" s="66">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C46" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C47" s="69"/>
-      <c r="D47" s="70">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="71"/>
-      <c r="D48" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="58"/>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="68">
-        <f>SUM(D50:D56)</f>
-        <v>0</v>
-      </c>
-      <c r="C51" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="D52" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="D53" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="D54" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C55" s="63" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="65"/>
-      <c r="D56" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="58"/>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="61" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="68">
-        <f>SUM(D58:D64)</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="63" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="D60" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C62" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C63" s="63" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="65"/>
-      <c r="D64" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D65" s="58"/>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="67" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="68">
-        <f>SUM(D66:D72)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="D67" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C68" s="63" t="s">
-        <v>77</v>
-      </c>
-      <c r="D68" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D69" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D70" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D71" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="65"/>
-      <c r="D72" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="58"/>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B74" s="67" t="s">
-        <v>65</v>
-      </c>
-      <c r="C74" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="68">
-        <f>SUM(D74:D80)</f>
-        <v>0</v>
-      </c>
-      <c r="C75" s="63" t="s">
-        <v>82</v>
-      </c>
-      <c r="D75" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="D76" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="D77" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="63"/>
-      <c r="D78" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C79" s="63"/>
-      <c r="D79" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="65"/>
-      <c r="D80" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="58"/>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="C82" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="D82" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="68">
-        <f>SUM(D82:D88)</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="D83" s="64">
-        <f>SUMIF($D$11:$D$32,C83,$F$11:$F$32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C84" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="D84" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C85" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="D85" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C86" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="D86" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C87" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="D87" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C88" s="65"/>
-      <c r="D88" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B90" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="C90" s="61"/>
-      <c r="D90" s="62">
-        <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="H9:K9"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D32">
-      <formula1>INDIRECT(C11)</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Modelo!$R$3:$R$14</xm:f>
@@ -18298,10 +18594,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -18314,7 +18610,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -18344,7 +18640,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -18403,31 +18699,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jul!F7</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -19378,10 +19674,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -19394,7 +19690,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -19422,7 +19718,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -19481,31 +19777,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Ago!F7</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>419.81999999999925</v>
+        <v>-2574.5100000000011</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="170" t="s">
+      <c r="B9" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="H9" s="173" t="s">
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>

--- a/arquivos extras/Planilha.xlsx
+++ b/arquivos extras/Planilha.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Mar" sheetId="11" r:id="rId3"/>
     <sheet name="Abr" sheetId="12" r:id="rId4"/>
     <sheet name="Mai" sheetId="13" r:id="rId5"/>
-    <sheet name="Jul" sheetId="4" r:id="rId6"/>
-    <sheet name="Jun" sheetId="14" r:id="rId7"/>
+    <sheet name="Jun" sheetId="14" r:id="rId6"/>
+    <sheet name="Jul" sheetId="4" r:id="rId7"/>
     <sheet name="Ago" sheetId="5" r:id="rId8"/>
     <sheet name="Set" sheetId="6" r:id="rId9"/>
     <sheet name="Out" sheetId="7" r:id="rId10"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="255">
   <si>
     <t>JAN</t>
   </si>
@@ -833,6 +833,24 @@
   </si>
   <si>
     <t>pc - bruto</t>
+  </si>
+  <si>
+    <t>pc - ventuinhas</t>
+  </si>
+  <si>
+    <t>pc - ram</t>
+  </si>
+  <si>
+    <t>mãe</t>
+  </si>
+  <si>
+    <t>spotify já foi pago</t>
+  </si>
+  <si>
+    <t>barbeiro</t>
+  </si>
+  <si>
+    <t>gasolina</t>
   </si>
 </sst>
 </file>
@@ -2108,6 +2126,27 @@
     <xf numFmtId="44" fontId="0" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="17" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2143,27 +2182,6 @@
     </xf>
     <xf numFmtId="44" fontId="11" fillId="26" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="17" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2775,7 +2793,9 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -2826,7 +2846,7 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>330.1</c:v>
+                  <c:v>336.90000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2835,7 +2855,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>302.22000000000003</c:v>
+                  <c:v>358.62</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>500</c:v>
@@ -2850,7 +2870,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3945.2699999999995</c:v>
+                  <c:v>5891.82</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3839,10 +3859,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -3891,7 +3911,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -3959,19 +3979,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>135</v>
       </c>
@@ -5078,10 +5098,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -5094,7 +5114,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -5122,7 +5142,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -5181,31 +5201,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Set!F7</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -6156,10 +6176,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -6172,7 +6192,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -6200,7 +6220,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -6259,31 +6279,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Out!F7</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -7239,10 +7259,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
       <c r="N2"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7256,7 +7276,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -7285,7 +7305,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -7347,14 +7367,14 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Nov!F7</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="N7"/>
     </row>
@@ -7362,19 +7382,19 @@
       <c r="N8"/>
     </row>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -8301,7 +8321,8 @@
     <col min="3" max="3" width="15.5703125" style="43" customWidth="1"/>
     <col min="4" max="5" width="14.140625" style="43" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="43" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.140625" style="43" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="43" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="43" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.85546875" style="43" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.140625" style="43" bestFit="1" customWidth="1"/>
@@ -8380,39 +8401,39 @@
       </c>
       <c r="G3" s="124">
         <f>Mai!$F$3</f>
-        <v>1879.2399999999993</v>
+        <v>4523.74</v>
       </c>
       <c r="H3" s="124">
         <f>Jun!$F$3</f>
-        <v>-2224.5100000000011</v>
+        <v>-8.3000000000004093</v>
       </c>
       <c r="I3" s="124">
         <f>Jul!$F$3</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="J3" s="124">
         <f>Ago!$F$3</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="K3" s="124">
         <f>Set!$F$3</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="L3" s="124">
         <f>Out!$F$3</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="M3" s="124">
         <f>Nov!$F$3</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="N3" s="125">
         <f>Dez!$F$3</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="O3" s="125">
         <f>SUM(C3:N3)</f>
-        <v>-6504.4000000000106</v>
+        <v>6795.529999999997</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8437,7 +8458,7 @@
       </c>
       <c r="G4" s="126">
         <f>Mai!$F$4</f>
-        <v>3687.9200000000005</v>
+        <v>3935.01</v>
       </c>
       <c r="H4" s="126">
         <f>Jun!$F$4</f>
@@ -8469,7 +8490,7 @@
       </c>
       <c r="O4" s="127">
         <f t="shared" ref="O4:O10" si="0">SUM(C4:N4)</f>
-        <v>7094.26</v>
+        <v>7341.35</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8494,11 +8515,11 @@
       </c>
       <c r="G5" s="128">
         <f>Mai!$F$6</f>
-        <v>498.83</v>
+        <v>597.03</v>
       </c>
       <c r="H5" s="128">
         <f>Jun!$F$6</f>
-        <v>0</v>
+        <v>809.6733333333334</v>
       </c>
       <c r="I5" s="128">
         <f>Jul!$F$6</f>
@@ -8526,7 +8547,7 @@
       </c>
       <c r="O5" s="129">
         <f t="shared" si="0"/>
-        <v>2149.3200000000002</v>
+        <v>3057.1933333333336</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8665,11 +8686,11 @@
       </c>
       <c r="G8" s="132">
         <f t="shared" si="1"/>
-        <v>4186.7500000000009</v>
+        <v>4532.04</v>
       </c>
       <c r="H8" s="132">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>1159.6733333333334</v>
       </c>
       <c r="I8" s="132">
         <f t="shared" si="1"/>
@@ -8697,7 +8718,7 @@
       </c>
       <c r="O8" s="133">
         <f t="shared" si="0"/>
-        <v>9243.5800000000017</v>
+        <v>10398.543333333333</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -8722,39 +8743,39 @@
       </c>
       <c r="G9" s="134">
         <f t="shared" si="2"/>
-        <v>-2307.5100000000016</v>
+        <v>-8.3000000000001819</v>
       </c>
       <c r="H9" s="134">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I9" s="134">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="J9" s="134">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="K9" s="134">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="L9" s="134">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="M9" s="134">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="N9" s="135">
         <f t="shared" si="2"/>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="O9" s="135">
         <f>N9</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -8945,7 +8966,7 @@
       </c>
       <c r="G17" s="101">
         <f>Mai!$B$42</f>
-        <v>44.7</v>
+        <v>69.7</v>
       </c>
       <c r="H17" s="102">
         <f>Jun!$B$42</f>
@@ -8977,7 +8998,7 @@
       </c>
       <c r="O17" s="109">
         <f t="shared" ref="O17:O23" si="3">SUM(C17:N17)</f>
-        <v>345.58</v>
+        <v>370.58</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
@@ -9230,7 +9251,7 @@
       </c>
       <c r="G22" s="101">
         <f>Mai!$D$90</f>
-        <v>3393.6299999999997</v>
+        <v>5340.1799999999994</v>
       </c>
       <c r="H22" s="101">
         <f>Jun!$D$90</f>
@@ -9353,15 +9374,15 @@
         <f>SUBTOTAL(9,Jan!I35,Fev!I35,Mar!I35,Abr!I35,Mai!I35,Jun!I35,Jul!I35,Ago!I35,Set!I35,Out!I35,Nov!I35,Dez!I35)</f>
         <v>30</v>
       </c>
-      <c r="I28" s="167" t="s">
+      <c r="I28" s="174" t="s">
         <v>194</v>
       </c>
-      <c r="J28" s="168"/>
-      <c r="K28" s="168"/>
-      <c r="L28" s="169"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="175"/>
+      <c r="L28" s="176"/>
       <c r="M28" s="151">
         <f>SUM(L30:L43)-SUM(K30:K43)</f>
-        <v>3215.99</v>
+        <v>3319.99</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -9378,7 +9399,7 @@
       </c>
       <c r="G29" s="64">
         <f>SUBTOTAL(9,Jan!I36,Fev!I36,Mar!I36,Abr!I36,Mai!I36,Jun!I36,Jul!I36,Ago!I36,Set!I36,Out!I36,Nov!I36,Dez!I36)</f>
-        <v>330.1</v>
+        <v>336.90000000000003</v>
       </c>
       <c r="I29" s="155" t="s">
         <v>195</v>
@@ -9412,16 +9433,16 @@
         <f>SUBTOTAL(9,Jan!I37,Fev!I37,Mar!I37,Abr!I37,Mai!I37,Jun!I37,Jul!I37,Ago!I37,Set!I37,Out!I37,Nov!I37,Dez!I37)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="175" t="s">
+      <c r="I30" s="163" t="s">
         <v>200</v>
       </c>
-      <c r="J30" s="176" t="s">
+      <c r="J30" s="164" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="176">
+      <c r="K30" s="164">
         <v>201.64</v>
       </c>
-      <c r="L30" s="176">
+      <c r="L30" s="164">
         <f>200.05+10+10+64</f>
         <v>284.05</v>
       </c>
@@ -9444,16 +9465,16 @@
         <f>SUBTOTAL(9,Jan!I38,Fev!I38,Mar!I38,Abr!I38,Mai!I38,Jun!I38,Jul!I38,Ago!I38,Set!I38,Out!I38,Nov!I38,Dez!I38)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="165" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="176" t="s">
+      <c r="J31" s="164" t="s">
         <v>203</v>
       </c>
-      <c r="K31" s="176">
+      <c r="K31" s="164">
         <v>1289.99</v>
       </c>
-      <c r="L31" s="176">
+      <c r="L31" s="164">
         <v>1517.64</v>
       </c>
       <c r="M31" s="154">
@@ -9470,18 +9491,18 @@
       </c>
       <c r="G32" s="64">
         <f>SUBTOTAL(9,Jan!I39,Fev!I39,Mar!I39,Abr!I39,Mai!I39,Jun!I39,Jul!I39,Ago!I39,Set!I39,Out!I39,Nov!I39,Dez!I39)</f>
-        <v>302.22000000000003</v>
-      </c>
-      <c r="I32" s="177" t="s">
+        <v>358.62</v>
+      </c>
+      <c r="I32" s="165" t="s">
         <v>204</v>
       </c>
-      <c r="J32" s="176" t="s">
+      <c r="J32" s="164" t="s">
         <v>205</v>
       </c>
-      <c r="K32" s="176">
+      <c r="K32" s="164">
         <v>700</v>
       </c>
-      <c r="L32" s="176">
+      <c r="L32" s="164">
         <v>1000</v>
       </c>
       <c r="M32" s="154">
@@ -9510,16 +9531,16 @@
       <c r="H33" s="43" t="s">
         <v>248</v>
       </c>
-      <c r="I33" s="177" t="s">
+      <c r="I33" s="165" t="s">
         <v>228</v>
       </c>
-      <c r="J33" s="176" t="s">
+      <c r="J33" s="164" t="s">
         <v>229</v>
       </c>
-      <c r="K33" s="176">
+      <c r="K33" s="164">
         <v>128</v>
       </c>
-      <c r="L33" s="176">
+      <c r="L33" s="164">
         <v>176</v>
       </c>
       <c r="M33" s="154">
@@ -9530,7 +9551,7 @@
     <row r="34" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="68">
         <f>SUM(D33:D40)</f>
-        <v>360.89</v>
+        <v>385.89</v>
       </c>
       <c r="C34" s="63" t="s">
         <v>22</v>
@@ -9547,19 +9568,19 @@
         <v>40</v>
       </c>
       <c r="H34" s="43">
-        <f>SUM(K30:K37)</f>
-        <v>7682.51</v>
-      </c>
-      <c r="I34" s="177" t="s">
+        <f>SUM(K30:K36)</f>
+        <v>4655.51</v>
+      </c>
+      <c r="I34" s="165" t="s">
         <v>230</v>
       </c>
-      <c r="J34" s="176" t="s">
+      <c r="J34" s="164" t="s">
         <v>229</v>
       </c>
-      <c r="K34" s="176">
+      <c r="K34" s="164">
         <v>320.74</v>
       </c>
-      <c r="L34" s="176">
+      <c r="L34" s="164">
         <v>385</v>
       </c>
       <c r="M34" s="154">
@@ -9583,16 +9604,16 @@
         <f>SUBTOTAL(9,Jan!I42,Fev!I42,Mar!I42,Abr!I42,Mai!I42,Jun!I42,Jul!I42,Ago!I42,Set!I42,Out!I42,Nov!I42,Dez!I42)</f>
         <v>877</v>
       </c>
-      <c r="I35" s="153" t="s">
+      <c r="I35" s="165" t="s">
         <v>231</v>
       </c>
-      <c r="J35" s="101" t="s">
+      <c r="J35" s="164" t="s">
         <v>241</v>
       </c>
-      <c r="K35" s="174">
+      <c r="K35" s="164">
         <v>1715.14</v>
       </c>
-      <c r="L35" s="152">
+      <c r="L35" s="164">
         <v>2017.8</v>
       </c>
       <c r="M35" s="154">
@@ -9622,15 +9643,15 @@
       <c r="J36" s="101" t="s">
         <v>240</v>
       </c>
-      <c r="K36" s="174">
-        <v>949</v>
+      <c r="K36" s="162">
+        <v>300</v>
       </c>
       <c r="L36" s="152">
-        <v>1045</v>
+        <v>500</v>
       </c>
       <c r="M36" s="154">
         <f t="shared" si="4"/>
-        <v>96</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
@@ -9647,7 +9668,7 @@
       </c>
       <c r="G37" s="64">
         <f>SUBTOTAL(9,C22:N22)</f>
-        <v>3945.2699999999995</v>
+        <v>5891.82</v>
       </c>
       <c r="I37" s="153" t="s">
         <v>233</v>
@@ -9655,7 +9676,7 @@
       <c r="J37" s="101" t="s">
         <v>240</v>
       </c>
-      <c r="K37" s="174">
+      <c r="K37" s="162">
         <v>2378</v>
       </c>
       <c r="L37" s="152">
@@ -9673,23 +9694,23 @@
       </c>
       <c r="D38" s="64">
         <f>SUBTOTAL(9,Fev!D46,Fev!D46,Mar!D46,Abr!D46,Mai!D46,Jun!D46,Jul!D46,Ago!D46,Set!D46,Out!D46,Nov!D46,Dez!D46)</f>
-        <v>158.01</v>
+        <v>183.01</v>
       </c>
       <c r="F38" s="75"/>
       <c r="G38" s="66">
         <f>SUBTOTAL(9,Jan!I45,Fev!I45,Mar!I45,Abr!I45,Mai!I45,Jun!I45,Jul!I45,Ago!I45,Set!I45,Out!I45,Nov!I45,Dez!I45)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="153" t="s">
+      <c r="I38" s="165" t="s">
         <v>243</v>
       </c>
-      <c r="J38" s="101" t="s">
+      <c r="J38" s="164" t="s">
         <v>240</v>
       </c>
-      <c r="K38" s="174">
+      <c r="K38" s="164">
         <v>78.900000000000006</v>
       </c>
-      <c r="L38" s="152">
+      <c r="L38" s="164">
         <v>93.24</v>
       </c>
       <c r="M38" s="154">
@@ -9704,16 +9725,16 @@
         <f>SUBTOTAL(9,Fev!D47,Fev!D47,Mar!D47,Abr!D47,Mai!D47,Jun!D47,Jul!D47,Ago!D47,Set!D47,Out!D47,Nov!D47,Dez!D47)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="177" t="s">
+      <c r="I39" s="165" t="s">
         <v>234</v>
       </c>
-      <c r="J39" s="176" t="s">
+      <c r="J39" s="164" t="s">
         <v>203</v>
       </c>
-      <c r="K39" s="176">
+      <c r="K39" s="164">
         <v>630</v>
       </c>
-      <c r="L39" s="176">
+      <c r="L39" s="164">
         <v>741</v>
       </c>
       <c r="M39" s="154">
@@ -9728,16 +9749,16 @@
         <f>SUBTOTAL(9,Fev!D48,Fev!D48,Mar!D48,Abr!D48,Mai!D48,Jun!D48,Jul!D48,Ago!D48,Set!D48,Out!D48,Nov!D48,Dez!D48)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="178" t="s">
+      <c r="I40" s="166" t="s">
         <v>239</v>
       </c>
-      <c r="J40" s="176" t="s">
+      <c r="J40" s="164" t="s">
         <v>238</v>
       </c>
-      <c r="K40" s="176">
+      <c r="K40" s="164">
         <v>394</v>
       </c>
-      <c r="L40" s="176">
+      <c r="L40" s="164">
         <v>765</v>
       </c>
       <c r="M40" s="154">
@@ -9749,16 +9770,16 @@
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
-      <c r="I41" s="153" t="s">
+      <c r="I41" s="165" t="s">
         <v>237</v>
       </c>
-      <c r="J41" s="101" t="s">
+      <c r="J41" s="164" t="s">
         <v>240</v>
       </c>
-      <c r="K41" s="174">
+      <c r="K41" s="164">
         <v>59.9</v>
       </c>
-      <c r="L41" s="152">
+      <c r="L41" s="164">
         <v>103.9</v>
       </c>
       <c r="M41" s="154">
@@ -9780,16 +9801,16 @@
       <c r="H42" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="I42" s="177" t="s">
+      <c r="I42" s="165" t="s">
         <v>235</v>
       </c>
-      <c r="J42" s="176" t="s">
+      <c r="J42" s="164" t="s">
         <v>238</v>
       </c>
-      <c r="K42" s="176">
+      <c r="K42" s="164">
         <v>175</v>
       </c>
-      <c r="L42" s="176">
+      <c r="L42" s="164">
         <v>373.58</v>
       </c>
       <c r="M42" s="154">
@@ -9813,16 +9834,16 @@
         <f>SUM(K38:K43)</f>
         <v>1444.5600000000002</v>
       </c>
-      <c r="I43" s="179" t="s">
+      <c r="I43" s="167" t="s">
         <v>236</v>
       </c>
-      <c r="J43" s="180" t="s">
+      <c r="J43" s="168" t="s">
         <v>238</v>
       </c>
-      <c r="K43" s="180">
+      <c r="K43" s="168">
         <v>106.76</v>
       </c>
-      <c r="L43" s="180">
+      <c r="L43" s="168">
         <v>171.85</v>
       </c>
       <c r="M43" s="161">
@@ -9849,16 +9870,16 @@
         <f>SUBTOTAL(9,Fev!D53,Fev!D53,Mar!D53,Abr!D53,Mai!D53,Jun!D53,Jul!D53,Ago!D53,Set!D53,Out!D53,Nov!D53,Dez!D53)</f>
         <v>142</v>
       </c>
-      <c r="I45" s="170" t="s">
+      <c r="I45" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="J45" s="171"/>
-      <c r="K45" s="171"/>
-      <c r="L45" s="172">
-        <f>SUM(K30:K43)</f>
-        <v>9127.07</v>
-      </c>
-      <c r="M45" s="173"/>
+      <c r="J45" s="178"/>
+      <c r="K45" s="178"/>
+      <c r="L45" s="179">
+        <f>SUM(H34,H43)</f>
+        <v>6100.0700000000006</v>
+      </c>
+      <c r="M45" s="180"/>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46"/>
@@ -10204,7 +10225,7 @@
       </c>
       <c r="D82" s="62">
         <f>SUBTOTAL(9,Fev!D90,Fev!D90,Mar!D90,Abr!D90,Mai!D90,Jun!D90,Jul!D90,Ago!D90,Set!D90,Out!D90,Nov!D90,Dez!D90)</f>
-        <v>3945.2699999999995</v>
+        <v>5891.82</v>
       </c>
     </row>
   </sheetData>
@@ -10383,19 +10404,19 @@
       </c>
     </row>
     <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="N9" s="49"/>
       <c r="P9" s="52" t="s">
         <v>65</v>
@@ -11394,10 +11415,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -11440,7 +11461,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -11511,19 +11532,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -12593,10 +12614,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -12639,7 +12660,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -12712,19 +12733,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -13804,10 +13825,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -13853,7 +13874,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -13933,19 +13954,19 @@
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -15076,10 +15097,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
       <c r="N2" t="s">
         <v>208</v>
       </c>
@@ -15095,14 +15116,14 @@
       <c r="C3" s="29"/>
       <c r="D3" s="30">
         <f>2500-O3-50</f>
-        <v>420</v>
+        <v>146</v>
       </c>
       <c r="E3" s="141" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="38">
-        <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>1879.2399999999993</v>
+        <f>SUM(D3,D5,D6,D7,D4,L3,N3,L5)</f>
+        <v>4523.74</v>
       </c>
       <c r="H3" s="116"/>
       <c r="I3" s="11" t="s">
@@ -15117,11 +15138,11 @@
       </c>
       <c r="N3" s="116">
         <f>L3-O3</f>
-        <v>473</v>
+        <v>199</v>
       </c>
       <c r="O3" s="116">
-        <f>300+500+150+400+50+630</f>
-        <v>2030</v>
+        <f>300+500+150+400+50+630+10+210+54</f>
+        <v>2304</v>
       </c>
       <c r="P3" s="116"/>
       <c r="Q3" s="116"/>
@@ -15139,12 +15160,12 @@
         <v>182</v>
       </c>
       <c r="F4" s="37">
-        <f>SUM(F11:F32)</f>
-        <v>3687.9200000000005</v>
+        <f>SUM(F11:F26)</f>
+        <v>3935.01</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>209</v>
@@ -15160,7 +15181,9 @@
         <v>6</v>
       </c>
       <c r="C5" s="25"/>
-      <c r="D5" s="27"/>
+      <c r="D5" s="27">
+        <v>60</v>
+      </c>
       <c r="E5" s="143" t="s">
         <v>183</v>
       </c>
@@ -15192,25 +15215,19 @@
       </c>
       <c r="F6" s="36">
         <f>SUM(K11:K22)</f>
-        <v>498.83</v>
+        <v>597.03</v>
       </c>
       <c r="I6" s="14">
-        <v>46163</v>
+        <v>46173</v>
       </c>
       <c r="K6" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="L6" s="158">
-        <f>322-147-F20-F21</f>
-        <v>83</v>
-      </c>
+      <c r="L6" s="158"/>
       <c r="M6" t="s">
         <v>188</v>
       </c>
-      <c r="O6" s="146">
-        <f>O3+L6</f>
-        <v>2113</v>
-      </c>
+      <c r="O6" s="146"/>
     </row>
     <row r="7" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
@@ -15225,27 +15242,27 @@
         <v>108</v>
       </c>
       <c r="F7" s="39">
-        <f>F3-F4-F6+L6</f>
-        <v>-2224.5100000000011</v>
+        <f>F3-F4-F6</f>
+        <v>-8.3000000000004093</v>
       </c>
       <c r="L7" s="116"/>
       <c r="P7" s="116"/>
     </row>
     <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -15325,7 +15342,8 @@
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="55">
-        <v>75.03</v>
+        <f>75.03+13.18+30+13.22</f>
+        <v>131.43</v>
       </c>
       <c r="M11" s="72"/>
       <c r="N11" s="91"/>
@@ -15358,7 +15376,8 @@
         <v>148</v>
       </c>
       <c r="K12" s="56">
-        <v>6.8</v>
+        <f>6.8+6.8</f>
+        <v>13.6</v>
       </c>
       <c r="M12" s="72"/>
       <c r="N12" s="91"/>
@@ -15475,10 +15494,16 @@
       <c r="F16" s="34">
         <v>69.900000000000006</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="13"/>
+      <c r="H16" s="19">
+        <v>46161</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>119</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="56"/>
+      <c r="K16" s="56">
+        <v>35</v>
+      </c>
       <c r="M16" s="72"/>
       <c r="N16" s="91"/>
       <c r="O16" s="82"/>
@@ -15646,10 +15671,17 @@
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="22"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="C24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>121</v>
+      </c>
       <c r="E24" s="7"/>
-      <c r="F24" s="34"/>
+      <c r="F24" s="34">
+        <f>4.58+9</f>
+        <v>13.58</v>
+      </c>
       <c r="M24" s="72"/>
       <c r="N24" s="91"/>
       <c r="O24" s="82"/>
@@ -15657,10 +15689,16 @@
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="22"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="34"/>
+      <c r="E25" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F25" s="34">
+        <v>208.51</v>
+      </c>
       <c r="M25" s="65"/>
       <c r="N25" s="92"/>
       <c r="O25" s="83"/>
@@ -15668,17 +15706,29 @@
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="22"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="C26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="34"/>
+      <c r="F26" s="34">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="22"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="34"/>
+      <c r="E27" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F27" s="34">
+        <v>1738.04</v>
+      </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="22"/>
@@ -15752,7 +15802,7 @@
       </c>
       <c r="I36" s="64">
         <f t="shared" ref="I36:I45" si="1">SUMIF($I$11:$I$22,H36,$K$11:$K$22)</f>
-        <v>36.799999999999997</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
@@ -15798,7 +15848,7 @@
       </c>
       <c r="I39" s="64">
         <f t="shared" si="1"/>
-        <v>75.03</v>
+        <v>131.43</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15834,7 +15884,7 @@
     <row r="42" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="68">
         <f>SUBTOTAL(9,D41:D48)</f>
-        <v>44.7</v>
+        <v>69.7</v>
       </c>
       <c r="C42" s="63" t="s">
         <v>22</v>
@@ -15903,7 +15953,7 @@
       </c>
       <c r="D46" s="64">
         <f t="shared" si="0"/>
-        <v>44.7</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
@@ -16279,7 +16329,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="62">
         <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>3393.6299999999997</v>
+        <v>5340.1799999999994</v>
       </c>
     </row>
   </sheetData>
@@ -16288,7 +16338,7 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="H9:K9"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D32">
       <formula1>INDIRECT(C11)</formula1>
     </dataValidation>
@@ -16296,7 +16346,7 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Modelo!$R$3:$R$14</xm:f>
@@ -16317,7 +16367,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Plan7">
+  <sheetPr codeName="Plan6">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P90"/>
@@ -16326,22 +16376,22 @@
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
     <col min="13" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>1</v>
@@ -16353,10 +16403,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -16369,7 +16419,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2574.5100000000011</v>
+        <v>-8.3000000000004093</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -16377,7 +16427,10 @@
       <c r="K3" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="118"/>
+      <c r="L3" s="118">
+        <f>Mai!L3</f>
+        <v>2503</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -16393,16 +16446,19 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="118"/>
+        <v>216</v>
+      </c>
+      <c r="L4" s="118">
+        <f>Mai!L4</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -16424,8 +16480,8 @@
         <v>179</v>
       </c>
       <c r="L5" s="118">
-        <f>SUM(P10:P25)</f>
-        <v>0</v>
+        <f>Mai!L5</f>
+        <v>156.5</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16439,7 +16495,7 @@
       </c>
       <c r="F6" s="36">
         <f>SUM(K11:K22)</f>
-        <v>0</v>
+        <v>809.6733333333334</v>
       </c>
       <c r="I6" s="14">
         <v>45847</v>
@@ -16455,32 +16511,32 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="28">
-        <f>Jun!F7</f>
-        <v>-2574.5100000000011</v>
+        <f>Mai!F7</f>
+        <v>-8.3000000000004093</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -16528,15 +16584,28 @@
       <c r="P10" s="55"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="33"/>
+      <c r="B11" s="22">
+        <v>46182</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="34">
+        <v>350</v>
+      </c>
       <c r="H11" s="18"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="55"/>
+      <c r="J11" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="K11" s="55">
+        <f>(130*4)+1738.04/6</f>
+        <v>809.6733333333334</v>
+      </c>
       <c r="M11" s="72"/>
       <c r="N11" s="91"/>
       <c r="O11" s="82"/>
@@ -16550,7 +16619,9 @@
       <c r="F12" s="34"/>
       <c r="H12" s="19"/>
       <c r="I12" s="13"/>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="K12" s="56"/>
       <c r="M12" s="72"/>
       <c r="N12" s="91"/>
@@ -16565,7 +16636,9 @@
       <c r="F13" s="34"/>
       <c r="H13" s="19"/>
       <c r="I13" s="13"/>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="K13" s="56"/>
       <c r="M13" s="72"/>
       <c r="N13" s="91"/>
@@ -16580,7 +16653,9 @@
       <c r="F14" s="34"/>
       <c r="H14" s="19"/>
       <c r="I14" s="13"/>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="K14" s="56"/>
       <c r="M14" s="72"/>
       <c r="N14" s="91"/>
@@ -16595,7 +16670,9 @@
       <c r="F15" s="34"/>
       <c r="H15" s="19"/>
       <c r="I15" s="13"/>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="K15" s="56"/>
       <c r="M15" s="72"/>
       <c r="N15" s="91"/>
@@ -16715,7 +16792,7 @@
       <c r="F23" s="34"/>
       <c r="K23" s="116">
         <f>SUM(K11:K22)</f>
-        <v>0</v>
+        <v>809.6733333333334</v>
       </c>
       <c r="M23" s="72"/>
       <c r="N23" s="91"/>
@@ -16728,6 +16805,15 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="34"/>
+      <c r="H24" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" t="s">
+        <v>222</v>
+      </c>
+      <c r="J24" s="159">
+        <v>1000</v>
+      </c>
       <c r="M24" s="72"/>
       <c r="N24" s="91"/>
       <c r="O24" s="82"/>
@@ -16739,6 +16825,9 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="34"/>
+      <c r="I25" t="s">
+        <v>221</v>
+      </c>
       <c r="M25" s="65"/>
       <c r="N25" s="92"/>
       <c r="O25" s="83"/>
@@ -16750,6 +16839,15 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="34"/>
+      <c r="H26" t="s">
+        <v>226</v>
+      </c>
+      <c r="I26" t="s">
+        <v>212</v>
+      </c>
+      <c r="J26" s="160">
+        <v>700</v>
+      </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="22"/>
@@ -16757,6 +16855,15 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="34"/>
+      <c r="H27" t="s">
+        <v>218</v>
+      </c>
+      <c r="I27" t="s">
+        <v>213</v>
+      </c>
+      <c r="J27" s="160">
+        <v>112</v>
+      </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="22"/>
@@ -16764,6 +16871,15 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="34"/>
+      <c r="H28" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" t="s">
+        <v>214</v>
+      </c>
+      <c r="J28" s="160">
+        <v>499</v>
+      </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="22"/>
@@ -16771,6 +16887,16 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="34"/>
+      <c r="H29" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" s="160">
+        <v>40</v>
+      </c>
+      <c r="K29" s="116"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="22"/>
@@ -16778,6 +16904,15 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="34"/>
+      <c r="H30" t="s">
+        <v>223</v>
+      </c>
+      <c r="I30" t="s">
+        <v>215</v>
+      </c>
+      <c r="J30" s="159">
+        <v>350</v>
+      </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="22"/>
@@ -16785,6 +16920,15 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="34"/>
+      <c r="H31" t="s">
+        <v>217</v>
+      </c>
+      <c r="I31" t="s">
+        <v>225</v>
+      </c>
+      <c r="J31" s="159">
+        <v>150</v>
+      </c>
     </row>
     <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="23"/>
@@ -16792,6 +16936,10 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="35"/>
+      <c r="J32" s="146">
+        <f>SUM(J24:J31)</f>
+        <v>2851</v>
+      </c>
     </row>
     <row r="34" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -17357,7 +17505,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="62">
         <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -17395,7 +17543,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Plan6">
+  <sheetPr codeName="Plan7">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P90"/>
@@ -17404,22 +17552,22 @@
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
     <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>1</v>
@@ -17431,10 +17579,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -17447,7 +17595,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2224.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -17455,10 +17603,7 @@
       <c r="K3" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="118">
-        <f>Mai!L3</f>
-        <v>2503</v>
-      </c>
+      <c r="L3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
@@ -17474,19 +17619,16 @@
       </c>
       <c r="F4" s="37">
         <f>SUM(F11:F32)</f>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
-        <v>216</v>
-      </c>
-      <c r="L4" s="118">
-        <f>Mai!L4</f>
-        <v>0</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
@@ -17508,8 +17650,8 @@
         <v>179</v>
       </c>
       <c r="L5" s="118">
-        <f>Mai!L5</f>
-        <v>156.5</v>
+        <f>SUM(P10:P25)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -17539,32 +17681,32 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="28">
-        <f>Mai!F7</f>
-        <v>-2224.5100000000011</v>
+        <f>Jun!F7</f>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -17612,19 +17754,11 @@
       <c r="P10" s="55"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="22">
-        <v>46182</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="34">
-        <v>350</v>
-      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="33"/>
       <c r="H11" s="18"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -17820,15 +17954,6 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="34"/>
-      <c r="H24" t="s">
-        <v>224</v>
-      </c>
-      <c r="I24" t="s">
-        <v>222</v>
-      </c>
-      <c r="J24" s="159">
-        <v>1000</v>
-      </c>
       <c r="M24" s="72"/>
       <c r="N24" s="91"/>
       <c r="O24" s="82"/>
@@ -17840,9 +17965,6 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="34"/>
-      <c r="I25" t="s">
-        <v>221</v>
-      </c>
       <c r="M25" s="65"/>
       <c r="N25" s="92"/>
       <c r="O25" s="83"/>
@@ -17854,15 +17976,6 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="34"/>
-      <c r="H26" t="s">
-        <v>226</v>
-      </c>
-      <c r="I26" t="s">
-        <v>212</v>
-      </c>
-      <c r="J26" s="160">
-        <v>700</v>
-      </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="22"/>
@@ -17870,15 +17983,6 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="34"/>
-      <c r="H27" t="s">
-        <v>218</v>
-      </c>
-      <c r="I27" t="s">
-        <v>213</v>
-      </c>
-      <c r="J27" s="160">
-        <v>112</v>
-      </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="22"/>
@@ -17886,15 +17990,6 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="34"/>
-      <c r="H28" t="s">
-        <v>217</v>
-      </c>
-      <c r="I28" t="s">
-        <v>214</v>
-      </c>
-      <c r="J28" s="160">
-        <v>499</v>
-      </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="22"/>
@@ -17902,16 +17997,6 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="34"/>
-      <c r="H29" t="s">
-        <v>219</v>
-      </c>
-      <c r="I29" t="s">
-        <v>220</v>
-      </c>
-      <c r="J29" s="160">
-        <v>40</v>
-      </c>
-      <c r="K29" s="116"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="22"/>
@@ -17919,15 +18004,6 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="34"/>
-      <c r="H30" t="s">
-        <v>223</v>
-      </c>
-      <c r="I30" t="s">
-        <v>215</v>
-      </c>
-      <c r="J30" s="159">
-        <v>350</v>
-      </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="22"/>
@@ -17935,15 +18011,6 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="34"/>
-      <c r="H31" t="s">
-        <v>217</v>
-      </c>
-      <c r="I31" t="s">
-        <v>225</v>
-      </c>
-      <c r="J31" s="159">
-        <v>150</v>
-      </c>
     </row>
     <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="23"/>
@@ -17951,10 +18018,6 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="35"/>
-      <c r="J32" s="146">
-        <f>SUM(J24:J31)</f>
-        <v>2851</v>
-      </c>
     </row>
     <row r="34" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -18520,7 +18583,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="62">
         <f>SUMIF(C11:C32,B90,F11:F32)</f>
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18594,10 +18657,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -18610,7 +18673,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -18640,7 +18703,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -18699,31 +18762,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Jul!F7</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
@@ -19674,10 +19737,10 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
@@ -19690,7 +19753,7 @@
       </c>
       <c r="F3" s="38">
         <f>SUM(D3,D5,D6,D7,D4)</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>5</v>
@@ -19718,7 +19781,7 @@
       </c>
       <c r="I4" s="15">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="K4" s="117" t="s">
         <v>167</v>
@@ -19777,31 +19840,31 @@
       <c r="C7" s="9"/>
       <c r="D7" s="28">
         <f>Ago!F7</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
       <c r="E7" s="145" t="s">
         <v>108</v>
       </c>
       <c r="F7" s="39">
         <f>F3-F4-F6</f>
-        <v>-2574.5100000000011</v>
+        <v>-1167.9733333333338</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="165" t="s">
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="H9" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
       <c r="M9" s="86" t="s">
         <v>110</v>
       </c>
